--- a/research/traditional_assets/database/data/senegal/senegal_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/senegal/senegal_telecom_services.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1008885905734616</v>
+        <v>0.1006174248017412</v>
       </c>
       <c r="C2">
-        <v>4491.409614711718</v>
+        <v>4451.367603947335</v>
       </c>
       <c r="D2">
-        <v>3924.609614711718</v>
+        <v>3929.240603947334</v>
       </c>
       <c r="E2">
-        <v>-680.1</v>
+        <v>-635.427</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>44.673</v>
       </c>
       <c r="G2">
         <v>566.8</v>
@@ -1445,28 +1445,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.2470519</v>
       </c>
       <c r="N2">
-        <v>958.3000000000001</v>
+        <v>956.0529481000001</v>
       </c>
       <c r="O2">
-        <v>287.49</v>
+        <v>286.81588443</v>
       </c>
       <c r="P2">
-        <v>670.8100000000001</v>
+        <v>669.23706367</v>
       </c>
       <c r="Q2">
-        <v>1036.91</v>
+        <v>1035.33706367</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1008885905734616</v>
+        <v>0.1012781058603446</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.5365156846091585</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>426.4699004059498</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1006174248017412</v>
+        <v>0.1003462590300208</v>
       </c>
       <c r="C3">
-        <v>4451.367603947335</v>
+        <v>4411.336535110622</v>
       </c>
       <c r="D3">
-        <v>3929.240603947334</v>
+        <v>3933.882535110623</v>
       </c>
       <c r="E3">
-        <v>-635.427</v>
+        <v>-590.754</v>
       </c>
       <c r="F3">
-        <v>44.673</v>
+        <v>89.346</v>
       </c>
       <c r="G3">
         <v>566.8</v>
@@ -1527,28 +1527,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M3">
-        <v>2.2470519</v>
+        <v>4.4941038</v>
       </c>
       <c r="N3">
-        <v>956.0529481000001</v>
+        <v>953.8058962000001</v>
       </c>
       <c r="O3">
-        <v>286.81588443</v>
+        <v>286.14176886</v>
       </c>
       <c r="P3">
-        <v>669.23706367</v>
+        <v>667.6641273400001</v>
       </c>
       <c r="Q3">
-        <v>1035.33706367</v>
+        <v>1033.76412734</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1012781058603446</v>
+        <v>0.1016755704387967</v>
       </c>
       <c r="T3">
-        <v>0.5365156846091585</v>
+        <v>0.5403594708579704</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>426.4699004059498</v>
+        <v>213.2349502029749</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1003462590300208</v>
+        <v>0.1000750932583004</v>
       </c>
       <c r="C4">
-        <v>4411.336535110622</v>
+        <v>4371.316447027218</v>
       </c>
       <c r="D4">
-        <v>3933.882535110623</v>
+        <v>3938.535447027218</v>
       </c>
       <c r="E4">
-        <v>-590.754</v>
+        <v>-546.081</v>
       </c>
       <c r="F4">
-        <v>89.346</v>
+        <v>134.019</v>
       </c>
       <c r="G4">
         <v>566.8</v>
@@ -1609,28 +1609,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M4">
-        <v>4.4941038</v>
+        <v>6.7411557</v>
       </c>
       <c r="N4">
-        <v>953.8058962000001</v>
+        <v>951.5588443</v>
       </c>
       <c r="O4">
-        <v>286.14176886</v>
+        <v>285.46765329</v>
       </c>
       <c r="P4">
-        <v>667.6641273400001</v>
+        <v>666.0911910100001</v>
       </c>
       <c r="Q4">
-        <v>1033.76412734</v>
+        <v>1032.19119101</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1016755704387967</v>
+        <v>0.1020812301631963</v>
       </c>
       <c r="T4">
-        <v>0.5403594708579704</v>
+        <v>0.5442825104315</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>213.2349502029749</v>
+        <v>142.1566334686499</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1000750932583004</v>
+        <v>0.09980392748658004</v>
       </c>
       <c r="C5">
-        <v>4371.316447027218</v>
+        <v>4331.307378706656</v>
       </c>
       <c r="D5">
-        <v>3938.535447027218</v>
+        <v>3943.199378706656</v>
       </c>
       <c r="E5">
-        <v>-546.081</v>
+        <v>-501.408</v>
       </c>
       <c r="F5">
-        <v>134.019</v>
+        <v>178.692</v>
       </c>
       <c r="G5">
         <v>566.8</v>
@@ -1691,28 +1691,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M5">
-        <v>6.7411557</v>
+        <v>8.988207599999999</v>
       </c>
       <c r="N5">
-        <v>951.5588443</v>
+        <v>949.3117924000001</v>
       </c>
       <c r="O5">
-        <v>285.46765329</v>
+        <v>284.79353772</v>
       </c>
       <c r="P5">
-        <v>666.0911910100001</v>
+        <v>664.51825468</v>
       </c>
       <c r="Q5">
-        <v>1032.19119101</v>
+        <v>1030.61825468</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1020812301631963</v>
+        <v>0.1024953411318542</v>
       </c>
       <c r="T5">
-        <v>0.5442825104315</v>
+        <v>0.5482872799961448</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>142.1566334686499</v>
+        <v>106.6174751014874</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09980392748658004</v>
+        <v>0.09953276171485965</v>
       </c>
       <c r="C6">
-        <v>4331.307378706656</v>
+        <v>4291.309369343474</v>
       </c>
       <c r="D6">
-        <v>3943.199378706656</v>
+        <v>3947.874369343474</v>
       </c>
       <c r="E6">
-        <v>-501.408</v>
+        <v>-456.735</v>
       </c>
       <c r="F6">
-        <v>178.692</v>
+        <v>223.365</v>
       </c>
       <c r="G6">
         <v>566.8</v>
@@ -1773,28 +1773,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M6">
-        <v>8.988207599999999</v>
+        <v>11.2352595</v>
       </c>
       <c r="N6">
-        <v>949.3117924000001</v>
+        <v>947.0647405000001</v>
       </c>
       <c r="O6">
-        <v>284.79353772</v>
+        <v>284.11942215</v>
       </c>
       <c r="P6">
-        <v>664.51825468</v>
+        <v>662.9453183500001</v>
       </c>
       <c r="Q6">
-        <v>1030.61825468</v>
+        <v>1029.04531835</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1024953411318542</v>
+        <v>0.1029181702261681</v>
       </c>
       <c r="T6">
-        <v>0.5482872799961448</v>
+        <v>0.5523763604989926</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>106.6174751014874</v>
+        <v>85.29398008118994</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09953276171485965</v>
+        <v>0.09926159594313927</v>
       </c>
       <c r="C7">
-        <v>4291.309369343474</v>
+        <v>4251.322458318298</v>
       </c>
       <c r="D7">
-        <v>3947.874369343474</v>
+        <v>3952.560458318298</v>
       </c>
       <c r="E7">
-        <v>-456.735</v>
+        <v>-412.062</v>
       </c>
       <c r="F7">
-        <v>223.365</v>
+        <v>268.038</v>
       </c>
       <c r="G7">
         <v>566.8</v>
@@ -1855,28 +1855,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M7">
-        <v>11.2352595</v>
+        <v>13.4823114</v>
       </c>
       <c r="N7">
-        <v>947.0647405000001</v>
+        <v>944.8176886000001</v>
       </c>
       <c r="O7">
-        <v>284.11942215</v>
+        <v>283.44530658</v>
       </c>
       <c r="P7">
-        <v>662.9453183500001</v>
+        <v>661.37238202</v>
       </c>
       <c r="Q7">
-        <v>1029.04531835</v>
+        <v>1027.47238202</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1029181702261681</v>
+        <v>0.1033499956841907</v>
       </c>
       <c r="T7">
-        <v>0.5523763604989926</v>
+        <v>0.5565524427146671</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>85.29398008118994</v>
+        <v>71.07831673432496</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09926159594313927</v>
+        <v>0.0989904301714189</v>
       </c>
       <c r="C8">
-        <v>4251.322458318298</v>
+        <v>4211.346685198958</v>
       </c>
       <c r="D8">
-        <v>3952.560458318298</v>
+        <v>3957.257685198958</v>
       </c>
       <c r="E8">
-        <v>-412.062</v>
+        <v>-367.3890000000001</v>
       </c>
       <c r="F8">
-        <v>268.038</v>
+        <v>312.711</v>
       </c>
       <c r="G8">
         <v>566.8</v>
@@ -1937,28 +1937,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M8">
-        <v>13.4823114</v>
+        <v>15.7293633</v>
       </c>
       <c r="N8">
-        <v>944.8176886000001</v>
+        <v>942.5706367</v>
       </c>
       <c r="O8">
-        <v>283.44530658</v>
+        <v>282.77119101</v>
       </c>
       <c r="P8">
-        <v>661.37238202</v>
+        <v>659.7994456900001</v>
       </c>
       <c r="Q8">
-        <v>1027.47238202</v>
+        <v>1025.89944569</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1033499956841907</v>
+        <v>0.1037911077112031</v>
       </c>
       <c r="T8">
-        <v>0.5565524427146671</v>
+        <v>0.5608183331500335</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>71.07831673432496</v>
+        <v>60.92427148656425</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09899043017141888</v>
+        <v>0.0987192643996985</v>
       </c>
       <c r="C9">
-        <v>4211.346685198959</v>
+        <v>4171.382089741597</v>
       </c>
       <c r="D9">
-        <v>3957.257685198959</v>
+        <v>3961.966089741597</v>
       </c>
       <c r="E9">
-        <v>-367.389</v>
+        <v>-322.716</v>
       </c>
       <c r="F9">
-        <v>312.7110000000001</v>
+        <v>357.384</v>
       </c>
       <c r="G9">
         <v>566.8</v>
@@ -2019,28 +2019,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M9">
-        <v>15.7293633</v>
+        <v>17.9764152</v>
       </c>
       <c r="N9">
-        <v>942.5706367</v>
+        <v>940.3235848</v>
       </c>
       <c r="O9">
-        <v>282.77119101</v>
+        <v>282.09707544</v>
       </c>
       <c r="P9">
-        <v>659.7994456900001</v>
+        <v>658.22650936</v>
       </c>
       <c r="Q9">
-        <v>1025.89944569</v>
+        <v>1024.32650936</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1037911077112031</v>
+        <v>0.1042418091301071</v>
       </c>
       <c r="T9">
-        <v>0.5608183331500335</v>
+        <v>0.5651769603339948</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>60.92427148656423</v>
+        <v>53.30873755074372</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0987192643996985</v>
+        <v>0.09844809862797813</v>
       </c>
       <c r="C10">
-        <v>4171.382089741597</v>
+        <v>4131.428711891791</v>
       </c>
       <c r="D10">
-        <v>3961.966089741597</v>
+        <v>3966.685711891791</v>
       </c>
       <c r="E10">
-        <v>-322.716</v>
+        <v>-278.043</v>
       </c>
       <c r="F10">
-        <v>357.384</v>
+        <v>402.057</v>
       </c>
       <c r="G10">
         <v>566.8</v>
@@ -2101,28 +2101,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M10">
-        <v>17.9764152</v>
+        <v>20.2234671</v>
       </c>
       <c r="N10">
-        <v>940.3235848</v>
+        <v>938.0765329000001</v>
       </c>
       <c r="O10">
-        <v>282.09707544</v>
+        <v>281.42295987</v>
       </c>
       <c r="P10">
-        <v>658.22650936</v>
+        <v>656.6535730300001</v>
       </c>
       <c r="Q10">
-        <v>1024.32650936</v>
+        <v>1022.75357303</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1042418091301071</v>
+        <v>0.1047024160747012</v>
       </c>
       <c r="T10">
-        <v>0.5651769603339948</v>
+        <v>0.5696313815219991</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>53.30873755074372</v>
+        <v>47.38554448954996</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09844809862797813</v>
+        <v>0.09817693285625774</v>
       </c>
       <c r="C11">
-        <v>4131.428711891791</v>
+        <v>4091.486591785682</v>
       </c>
       <c r="D11">
-        <v>3966.685711891791</v>
+        <v>3971.416591785682</v>
       </c>
       <c r="E11">
-        <v>-278.043</v>
+        <v>-233.3700000000001</v>
       </c>
       <c r="F11">
-        <v>402.057</v>
+        <v>446.73</v>
       </c>
       <c r="G11">
         <v>566.8</v>
@@ -2183,28 +2183,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M11">
-        <v>20.2234671</v>
+        <v>22.470519</v>
       </c>
       <c r="N11">
-        <v>938.0765329000001</v>
+        <v>935.8294810000001</v>
       </c>
       <c r="O11">
-        <v>281.42295987</v>
+        <v>280.7488443</v>
       </c>
       <c r="P11">
-        <v>656.6535730300001</v>
+        <v>655.0806367</v>
       </c>
       <c r="Q11">
-        <v>1022.75357303</v>
+        <v>1021.1806367</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1047024160747012</v>
+        <v>0.1051732587291753</v>
       </c>
       <c r="T11">
-        <v>0.5696313815219991</v>
+        <v>0.5741847898475148</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>47.38554448954996</v>
+        <v>42.64699004059498</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09817693285625774</v>
+        <v>0.09790576708453737</v>
       </c>
       <c r="C12">
-        <v>4091.486591785682</v>
+        <v>4051.555769751117</v>
       </c>
       <c r="D12">
-        <v>3971.416591785682</v>
+        <v>3976.158769751117</v>
       </c>
       <c r="E12">
-        <v>-233.37</v>
+        <v>-188.697</v>
       </c>
       <c r="F12">
-        <v>446.73</v>
+        <v>491.403</v>
       </c>
       <c r="G12">
         <v>566.8</v>
@@ -2265,28 +2265,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M12">
-        <v>22.470519</v>
+        <v>24.7175709</v>
       </c>
       <c r="N12">
-        <v>935.8294810000001</v>
+        <v>933.5824291000001</v>
       </c>
       <c r="O12">
-        <v>280.7488443</v>
+        <v>280.07472873</v>
       </c>
       <c r="P12">
-        <v>655.0806367</v>
+        <v>653.5077003700001</v>
       </c>
       <c r="Q12">
-        <v>1021.1806367</v>
+        <v>1019.60770037</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1051732587291753</v>
+        <v>0.1056546821174577</v>
       </c>
       <c r="T12">
-        <v>0.5741847898475148</v>
+        <v>0.5788405219556262</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>42.64699004059497</v>
+        <v>38.76999094599543</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09790576708453737</v>
+        <v>0.09763460131281695</v>
       </c>
       <c r="C13">
-        <v>4051.555769751117</v>
+        <v>4011.636286308788</v>
       </c>
       <c r="D13">
-        <v>3976.158769751117</v>
+        <v>3980.912286308788</v>
       </c>
       <c r="E13">
-        <v>-188.697</v>
+        <v>-144.024</v>
       </c>
       <c r="F13">
-        <v>491.403</v>
+        <v>536.076</v>
       </c>
       <c r="G13">
         <v>566.8</v>
@@ -2347,28 +2347,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M13">
-        <v>24.7175709</v>
+        <v>26.9646228</v>
       </c>
       <c r="N13">
-        <v>933.5824291000001</v>
+        <v>931.3353772</v>
       </c>
       <c r="O13">
-        <v>280.07472873</v>
+        <v>279.40061316</v>
       </c>
       <c r="P13">
-        <v>653.5077003700001</v>
+        <v>651.9347640400001</v>
       </c>
       <c r="Q13">
-        <v>1019.60770037</v>
+        <v>1018.03476404</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1056546821174577</v>
+        <v>0.1061470469463829</v>
       </c>
       <c r="T13">
-        <v>0.5788405219556262</v>
+        <v>0.5836020661571037</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>38.76999094599543</v>
+        <v>35.53915836716247</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09763460131281695</v>
+        <v>0.09736343554109658</v>
       </c>
       <c r="C14">
-        <v>4011.636286308788</v>
+        <v>3971.72818217339</v>
       </c>
       <c r="D14">
-        <v>3980.912286308788</v>
+        <v>3985.677182173391</v>
       </c>
       <c r="E14">
-        <v>-144.024</v>
+        <v>-99.351</v>
       </c>
       <c r="F14">
-        <v>536.076</v>
+        <v>580.749</v>
       </c>
       <c r="G14">
         <v>566.8</v>
@@ -2429,28 +2429,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M14">
-        <v>26.9646228</v>
+        <v>29.2116747</v>
       </c>
       <c r="N14">
-        <v>931.3353772</v>
+        <v>929.0883253000001</v>
       </c>
       <c r="O14">
-        <v>279.40061316</v>
+        <v>278.72649759</v>
       </c>
       <c r="P14">
-        <v>651.9347640400001</v>
+        <v>650.3618277100001</v>
       </c>
       <c r="Q14">
-        <v>1018.03476404</v>
+        <v>1016.46182771</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1061470469463829</v>
+        <v>0.1066507305070076</v>
       </c>
       <c r="T14">
-        <v>0.5836020661571037</v>
+        <v>0.5884730711448222</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>35.53915836716247</v>
+        <v>32.80537695430382</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09736343554109658</v>
+        <v>0.0970922697693762</v>
       </c>
       <c r="C15">
-        <v>3971.72818217339</v>
+        <v>3931.831498254787</v>
       </c>
       <c r="D15">
-        <v>3985.677182173391</v>
+        <v>3990.453498254787</v>
       </c>
       <c r="E15">
-        <v>-99.351</v>
+        <v>-54.67799999999988</v>
       </c>
       <c r="F15">
-        <v>580.749</v>
+        <v>625.4220000000001</v>
       </c>
       <c r="G15">
         <v>566.8</v>
@@ -2511,28 +2511,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M15">
-        <v>29.2116747</v>
+        <v>31.45872660000001</v>
       </c>
       <c r="N15">
-        <v>929.0883253000001</v>
+        <v>926.8412734000001</v>
       </c>
       <c r="O15">
-        <v>278.72649759</v>
+        <v>278.05238202</v>
       </c>
       <c r="P15">
-        <v>650.3618277100001</v>
+        <v>648.78889138</v>
       </c>
       <c r="Q15">
-        <v>1016.46182771</v>
+        <v>1014.88889138</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1066507305070076</v>
+        <v>0.1071661276388095</v>
       </c>
       <c r="T15">
-        <v>0.5884730711448222</v>
+        <v>0.5934573553183016</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>32.80537695430382</v>
+        <v>30.46213574328212</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0970922697693762</v>
+        <v>0.09682110399765581</v>
       </c>
       <c r="C16">
-        <v>3931.831498254787</v>
+        <v>3891.946275659173</v>
       </c>
       <c r="D16">
-        <v>3990.453498254787</v>
+        <v>3995.241275659173</v>
       </c>
       <c r="E16">
-        <v>-54.67799999999988</v>
+        <v>-10.00499999999988</v>
       </c>
       <c r="F16">
-        <v>625.4220000000001</v>
+        <v>670.0950000000001</v>
       </c>
       <c r="G16">
         <v>566.8</v>
@@ -2593,28 +2593,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M16">
-        <v>31.45872660000001</v>
+        <v>33.70577850000001</v>
       </c>
       <c r="N16">
-        <v>926.8412734000001</v>
+        <v>924.5942215</v>
       </c>
       <c r="O16">
-        <v>278.05238202</v>
+        <v>277.37826645</v>
       </c>
       <c r="P16">
-        <v>648.78889138</v>
+        <v>647.21595505</v>
       </c>
       <c r="Q16">
-        <v>1014.88889138</v>
+        <v>1013.31595505</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1071661276388095</v>
+        <v>0.107693651761948</v>
       </c>
       <c r="T16">
-        <v>0.5934573553183016</v>
+        <v>0.5985589167664511</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>30.46213574328212</v>
+        <v>28.43132669372997</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09682110399765581</v>
+        <v>0.09654993822593544</v>
       </c>
       <c r="C17">
-        <v>3891.946275659173</v>
+        <v>3852.072555690262</v>
       </c>
       <c r="D17">
-        <v>3995.241275659173</v>
+        <v>4000.040555690262</v>
       </c>
       <c r="E17">
-        <v>-10.005</v>
+        <v>34.66800000000001</v>
       </c>
       <c r="F17">
-        <v>670.095</v>
+        <v>714.768</v>
       </c>
       <c r="G17">
         <v>566.8</v>
@@ -2675,28 +2675,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M17">
-        <v>33.7057785</v>
+        <v>35.9528304</v>
       </c>
       <c r="N17">
-        <v>924.5942215000001</v>
+        <v>922.3471696</v>
       </c>
       <c r="O17">
-        <v>277.37826645</v>
+        <v>276.70415088</v>
       </c>
       <c r="P17">
-        <v>647.21595505</v>
+        <v>645.6430187200001</v>
       </c>
       <c r="Q17">
-        <v>1013.31595505</v>
+        <v>1011.74301872</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.107693651761948</v>
+        <v>0.1082337359832565</v>
       </c>
       <c r="T17">
-        <v>0.5985589167664511</v>
+        <v>0.603781943963366</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>28.43132669372998</v>
+        <v>26.65436877537186</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09654993822593544</v>
+        <v>0.09627877245421504</v>
       </c>
       <c r="C18">
-        <v>3852.072555690262</v>
+        <v>3812.21037985047</v>
       </c>
       <c r="D18">
-        <v>4000.040555690262</v>
+        <v>4004.851379850469</v>
       </c>
       <c r="E18">
-        <v>34.66800000000001</v>
+        <v>79.34100000000001</v>
       </c>
       <c r="F18">
-        <v>714.768</v>
+        <v>759.441</v>
       </c>
       <c r="G18">
         <v>566.8</v>
@@ -2757,28 +2757,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M18">
-        <v>35.9528304</v>
+        <v>38.1998823</v>
       </c>
       <c r="N18">
-        <v>922.3471696</v>
+        <v>920.1001177000001</v>
       </c>
       <c r="O18">
-        <v>276.70415088</v>
+        <v>276.03003531</v>
       </c>
       <c r="P18">
-        <v>645.6430187200001</v>
+        <v>644.07008239</v>
       </c>
       <c r="Q18">
-        <v>1011.74301872</v>
+        <v>1010.17008239</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1082337359832565</v>
+        <v>0.1087868342821868</v>
       </c>
       <c r="T18">
-        <v>0.603781943963366</v>
+        <v>0.609130827237315</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>26.65436877537186</v>
+        <v>25.08646472976175</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09627877245421504</v>
+        <v>0.09600760668249467</v>
       </c>
       <c r="C19">
-        <v>3812.21037985047</v>
+        <v>3772.359789842106</v>
       </c>
       <c r="D19">
-        <v>4004.851379850469</v>
+        <v>4009.673789842106</v>
       </c>
       <c r="E19">
-        <v>79.34100000000001</v>
+        <v>124.0140000000001</v>
       </c>
       <c r="F19">
-        <v>759.441</v>
+        <v>804.1140000000001</v>
       </c>
       <c r="G19">
         <v>566.8</v>
@@ -2839,28 +2839,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M19">
-        <v>38.1998823</v>
+        <v>40.44693420000001</v>
       </c>
       <c r="N19">
-        <v>920.1001177000001</v>
+        <v>917.8530658000001</v>
       </c>
       <c r="O19">
-        <v>276.03003531</v>
+        <v>275.35591974</v>
       </c>
       <c r="P19">
-        <v>644.07008239</v>
+        <v>642.4971460600001</v>
       </c>
       <c r="Q19">
-        <v>1010.17008239</v>
+        <v>1008.59714606</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1087868342821868</v>
+        <v>0.1093534227835301</v>
       </c>
       <c r="T19">
-        <v>0.609130827237315</v>
+        <v>0.6146101710789214</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>25.08646472976175</v>
+        <v>23.69277224477498</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09600760668249468</v>
+        <v>0.09573644091077427</v>
       </c>
       <c r="C20">
-        <v>3772.359789842106</v>
+        <v>3732.520827568595</v>
       </c>
       <c r="D20">
-        <v>4009.673789842106</v>
+        <v>4014.507827568596</v>
       </c>
       <c r="E20">
-        <v>124.014</v>
+        <v>168.687</v>
       </c>
       <c r="F20">
-        <v>804.114</v>
+        <v>848.787</v>
       </c>
       <c r="G20">
         <v>566.8</v>
@@ -2921,28 +2921,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M20">
-        <v>40.4469342</v>
+        <v>42.6939861</v>
       </c>
       <c r="N20">
-        <v>917.8530658000001</v>
+        <v>915.6060139000001</v>
       </c>
       <c r="O20">
-        <v>275.35591974</v>
+        <v>274.68180417</v>
       </c>
       <c r="P20">
-        <v>642.4971460600001</v>
+        <v>640.92420973</v>
       </c>
       <c r="Q20">
-        <v>1008.59714606</v>
+        <v>1007.02420973</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1093534227835301</v>
+        <v>0.1099340011244127</v>
       </c>
       <c r="T20">
-        <v>0.6146101710789214</v>
+        <v>0.6202248073610611</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>23.69277224477498</v>
+        <v>22.44578423189209</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09573644091077427</v>
+        <v>0.0954652751390539</v>
       </c>
       <c r="C21">
-        <v>3732.520827568595</v>
+        <v>3692.69353513567</v>
       </c>
       <c r="D21">
-        <v>4014.507827568596</v>
+        <v>4019.35353513567</v>
       </c>
       <c r="E21">
-        <v>168.687</v>
+        <v>213.36</v>
       </c>
       <c r="F21">
-        <v>848.787</v>
+        <v>893.46</v>
       </c>
       <c r="G21">
         <v>566.8</v>
@@ -3003,28 +3003,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M21">
-        <v>42.6939861</v>
+        <v>44.941038</v>
       </c>
       <c r="N21">
-        <v>915.6060139000001</v>
+        <v>913.358962</v>
       </c>
       <c r="O21">
-        <v>274.68180417</v>
+        <v>274.0076886</v>
       </c>
       <c r="P21">
-        <v>640.92420973</v>
+        <v>639.3512734000001</v>
       </c>
       <c r="Q21">
-        <v>1007.02420973</v>
+        <v>1005.4512734</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1099340011244127</v>
+        <v>0.1105290939238174</v>
       </c>
       <c r="T21">
-        <v>0.6202248073610611</v>
+        <v>0.6259798095502545</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>22.44578423189209</v>
+        <v>21.32349502029749</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0954652751390539</v>
+        <v>0.09519410936733351</v>
       </c>
       <c r="C22">
-        <v>3692.69353513567</v>
+        <v>3652.877954852609</v>
       </c>
       <c r="D22">
-        <v>4019.35353513567</v>
+        <v>4024.210954852609</v>
       </c>
       <c r="E22">
-        <v>213.36</v>
+        <v>258.0330000000001</v>
       </c>
       <c r="F22">
-        <v>893.46</v>
+        <v>938.1330000000002</v>
       </c>
       <c r="G22">
         <v>566.8</v>
@@ -3085,28 +3085,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M22">
-        <v>44.941038</v>
+        <v>47.18808990000001</v>
       </c>
       <c r="N22">
-        <v>913.358962</v>
+        <v>911.1119101</v>
       </c>
       <c r="O22">
-        <v>274.0076886</v>
+        <v>273.33357303</v>
       </c>
       <c r="P22">
-        <v>639.3512734000001</v>
+        <v>637.77833707</v>
       </c>
       <c r="Q22">
-        <v>1005.4512734</v>
+        <v>1003.87833707</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1105290939238174</v>
+        <v>0.1111392523637133</v>
       </c>
       <c r="T22">
-        <v>0.6259798095502545</v>
+        <v>0.6318805079974021</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>21.32349502029749</v>
+        <v>20.30809049552141</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0951941093673335</v>
+        <v>0.09492294359561311</v>
       </c>
       <c r="C23">
-        <v>3652.877954852609</v>
+        <v>3613.074129233459</v>
       </c>
       <c r="D23">
-        <v>4024.210954852609</v>
+        <v>4029.08012923346</v>
       </c>
       <c r="E23">
-        <v>258.033</v>
+        <v>302.706</v>
       </c>
       <c r="F23">
-        <v>938.133</v>
+        <v>982.806</v>
       </c>
       <c r="G23">
         <v>566.8</v>
@@ -3167,28 +3167,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M23">
-        <v>47.1880899</v>
+        <v>49.4351418</v>
       </c>
       <c r="N23">
-        <v>911.1119101</v>
+        <v>908.8648582000001</v>
       </c>
       <c r="O23">
-        <v>273.33357303</v>
+        <v>272.65945746</v>
       </c>
       <c r="P23">
-        <v>637.77833707</v>
+        <v>636.2054007400001</v>
       </c>
       <c r="Q23">
-        <v>1003.87833707</v>
+        <v>1002.30540074</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1111392523637133</v>
+        <v>0.1117650558918117</v>
       </c>
       <c r="T23">
-        <v>0.6318805079974019</v>
+        <v>0.6379325064047329</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>20.30809049552141</v>
+        <v>19.38499547299772</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09492294359561311</v>
+        <v>0.09465177782389274</v>
       </c>
       <c r="C24">
-        <v>3613.074129233459</v>
+        <v>3573.282100998283</v>
       </c>
       <c r="D24">
-        <v>4029.08012923346</v>
+        <v>4033.961100998283</v>
       </c>
       <c r="E24">
-        <v>302.706</v>
+        <v>347.379</v>
       </c>
       <c r="F24">
-        <v>982.806</v>
+        <v>1027.479</v>
       </c>
       <c r="G24">
         <v>566.8</v>
@@ -3249,28 +3249,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M24">
-        <v>49.4351418</v>
+        <v>51.6821937</v>
       </c>
       <c r="N24">
-        <v>908.8648582000001</v>
+        <v>906.6178063000001</v>
       </c>
       <c r="O24">
-        <v>272.65945746</v>
+        <v>271.98534189</v>
       </c>
       <c r="P24">
-        <v>636.2054007400001</v>
+        <v>634.63246441</v>
       </c>
       <c r="Q24">
-        <v>1002.30540074</v>
+        <v>1000.73246441</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1117650558918117</v>
+        <v>0.1124071140570035</v>
       </c>
       <c r="T24">
-        <v>0.6379325064047329</v>
+        <v>0.6441416995758904</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>19.38499547299772</v>
+        <v>18.54216958286738</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09465177782389274</v>
+        <v>0.09438061205217235</v>
       </c>
       <c r="C25">
-        <v>3573.282100998283</v>
+        <v>3533.501913074401</v>
       </c>
       <c r="D25">
-        <v>4033.961100998283</v>
+        <v>4038.853913074402</v>
       </c>
       <c r="E25">
-        <v>347.379</v>
+        <v>392.052</v>
       </c>
       <c r="F25">
-        <v>1027.479</v>
+        <v>1072.152</v>
       </c>
       <c r="G25">
         <v>566.8</v>
@@ -3331,28 +3331,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M25">
-        <v>51.6821937</v>
+        <v>53.9292456</v>
       </c>
       <c r="N25">
-        <v>906.6178063000001</v>
+        <v>904.3707544000001</v>
       </c>
       <c r="O25">
-        <v>271.98534189</v>
+        <v>271.31122632</v>
       </c>
       <c r="P25">
-        <v>634.63246441</v>
+        <v>633.0595280800001</v>
       </c>
       <c r="Q25">
-        <v>1000.73246441</v>
+        <v>999.1595280800001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1124071140570035</v>
+        <v>0.1130660684897005</v>
       </c>
       <c r="T25">
-        <v>0.6441416995758904</v>
+        <v>0.6505142925673417</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>18.54216958286738</v>
+        <v>17.76957918358124</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09438061205217235</v>
+        <v>0.09410944628045198</v>
       </c>
       <c r="C26">
-        <v>3533.501913074401</v>
+        <v>3493.733608597658</v>
       </c>
       <c r="D26">
-        <v>4038.853913074402</v>
+        <v>4043.758608597657</v>
       </c>
       <c r="E26">
-        <v>392.052</v>
+        <v>436.725</v>
       </c>
       <c r="F26">
-        <v>1072.152</v>
+        <v>1116.825</v>
       </c>
       <c r="G26">
         <v>566.8</v>
@@ -3413,28 +3413,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M26">
-        <v>53.9292456</v>
+        <v>56.1762975</v>
       </c>
       <c r="N26">
-        <v>904.3707544000001</v>
+        <v>902.1237025</v>
       </c>
       <c r="O26">
-        <v>271.31122632</v>
+        <v>270.63711075</v>
       </c>
       <c r="P26">
-        <v>633.0595280800001</v>
+        <v>631.4865917500001</v>
       </c>
       <c r="Q26">
-        <v>999.1595280800001</v>
+        <v>997.5865917500001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1130660684897005</v>
+        <v>0.1137425950406026</v>
       </c>
       <c r="T26">
-        <v>0.6505142925673417</v>
+        <v>0.6570568213718984</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>17.76957918358124</v>
+        <v>17.05879601623799</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09410944628045198</v>
+        <v>0.09383828050873157</v>
       </c>
       <c r="C27">
-        <v>3493.733608597658</v>
+        <v>3453.977230913682</v>
       </c>
       <c r="D27">
-        <v>4043.758608597657</v>
+        <v>4048.675230913682</v>
       </c>
       <c r="E27">
-        <v>436.725</v>
+        <v>481.398</v>
       </c>
       <c r="F27">
-        <v>1116.825</v>
+        <v>1161.498</v>
       </c>
       <c r="G27">
         <v>566.8</v>
@@ -3495,28 +3495,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M27">
-        <v>56.1762975</v>
+        <v>58.4233494</v>
       </c>
       <c r="N27">
-        <v>902.1237025</v>
+        <v>899.8766506000001</v>
       </c>
       <c r="O27">
-        <v>270.63711075</v>
+        <v>269.96299518</v>
       </c>
       <c r="P27">
-        <v>631.4865917500001</v>
+        <v>629.9136554200001</v>
       </c>
       <c r="Q27">
-        <v>997.5865917500001</v>
+        <v>996.0136554200001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1137425950406026</v>
+        <v>0.1144374060928805</v>
       </c>
       <c r="T27">
-        <v>0.6570568213718984</v>
+        <v>0.6637761752792807</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>17.05879601623799</v>
+        <v>16.40268847715191</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09383828050873157</v>
+        <v>0.09356711473701121</v>
       </c>
       <c r="C28">
-        <v>3453.977230913682</v>
+        <v>3414.232823579167</v>
       </c>
       <c r="D28">
-        <v>4048.675230913682</v>
+        <v>4053.603823579167</v>
       </c>
       <c r="E28">
-        <v>481.398</v>
+        <v>526.071</v>
       </c>
       <c r="F28">
-        <v>1161.498</v>
+        <v>1206.171</v>
       </c>
       <c r="G28">
         <v>566.8</v>
@@ -3577,28 +3577,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M28">
-        <v>58.4233494</v>
+        <v>60.6704013</v>
       </c>
       <c r="N28">
-        <v>899.8766506000001</v>
+        <v>897.6295987000001</v>
       </c>
       <c r="O28">
-        <v>269.96299518</v>
+        <v>269.28887961</v>
       </c>
       <c r="P28">
-        <v>629.9136554200001</v>
+        <v>628.34071909</v>
       </c>
       <c r="Q28">
-        <v>996.0136554200001</v>
+        <v>994.44071909</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1144374060928805</v>
+        <v>0.1151512530643989</v>
       </c>
       <c r="T28">
-        <v>0.6637761752792807</v>
+        <v>0.6706796210745367</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>16.40268847715191</v>
+        <v>15.79518149651666</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09356711473701121</v>
+        <v>0.09329594896529081</v>
       </c>
       <c r="C29">
-        <v>3414.232823579167</v>
+        <v>3374.500430363159</v>
       </c>
       <c r="D29">
-        <v>4053.603823579167</v>
+        <v>4058.544430363159</v>
       </c>
       <c r="E29">
-        <v>526.071</v>
+        <v>570.7440000000003</v>
       </c>
       <c r="F29">
-        <v>1206.171</v>
+        <v>1250.844</v>
       </c>
       <c r="G29">
         <v>566.8</v>
@@ -3659,28 +3659,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M29">
-        <v>60.6704013</v>
+        <v>62.91745320000001</v>
       </c>
       <c r="N29">
-        <v>897.6295987000001</v>
+        <v>895.3825468</v>
       </c>
       <c r="O29">
-        <v>269.28887961</v>
+        <v>268.61476404</v>
       </c>
       <c r="P29">
-        <v>628.34071909</v>
+        <v>626.76778276</v>
       </c>
       <c r="Q29">
-        <v>994.44071909</v>
+        <v>992.8677827600001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1151512530643989</v>
+        <v>0.1158849291184595</v>
       </c>
       <c r="T29">
-        <v>0.6706796210745367</v>
+        <v>0.6777748292529941</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>15.79518149651666</v>
+        <v>15.23106787164106</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09329594896529081</v>
+        <v>0.09302478319357042</v>
       </c>
       <c r="C30">
-        <v>3374.500430363159</v>
+        <v>3334.78009524835</v>
       </c>
       <c r="D30">
-        <v>4058.544430363159</v>
+        <v>4063.49709524835</v>
       </c>
       <c r="E30">
-        <v>570.7440000000003</v>
+        <v>615.4170000000003</v>
       </c>
       <c r="F30">
-        <v>1250.844</v>
+        <v>1295.517</v>
       </c>
       <c r="G30">
         <v>566.8</v>
@@ -3741,28 +3741,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M30">
-        <v>62.91745320000001</v>
+        <v>65.16450510000001</v>
       </c>
       <c r="N30">
-        <v>895.3825468</v>
+        <v>893.1354949</v>
       </c>
       <c r="O30">
-        <v>268.61476404</v>
+        <v>267.94064847</v>
       </c>
       <c r="P30">
-        <v>626.76778276</v>
+        <v>625.1948464300001</v>
       </c>
       <c r="Q30">
-        <v>992.8677827600001</v>
+        <v>991.2948464300001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1158849291184595</v>
+        <v>0.1166392721036203</v>
       </c>
       <c r="T30">
-        <v>0.6777748292529941</v>
+        <v>0.6850699024505632</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>15.23106787164106</v>
+        <v>14.70585863468792</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09302478319357042</v>
+        <v>0.09275361742185004</v>
       </c>
       <c r="C31">
-        <v>3334.78009524835</v>
+        <v>3295.071862432383</v>
       </c>
       <c r="D31">
-        <v>4063.49709524835</v>
+        <v>4068.461862432383</v>
       </c>
       <c r="E31">
-        <v>615.417</v>
+        <v>660.09</v>
       </c>
       <c r="F31">
-        <v>1295.517</v>
+        <v>1340.19</v>
       </c>
       <c r="G31">
         <v>566.8</v>
@@ -3823,28 +3823,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M31">
-        <v>65.1645051</v>
+        <v>67.411557</v>
       </c>
       <c r="N31">
-        <v>893.1354949</v>
+        <v>890.8884430000001</v>
       </c>
       <c r="O31">
-        <v>267.94064847</v>
+        <v>267.2665329</v>
       </c>
       <c r="P31">
-        <v>625.1948464300001</v>
+        <v>623.6219101</v>
       </c>
       <c r="Q31">
-        <v>991.2948464300001</v>
+        <v>989.7219101000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1166392721036203</v>
+        <v>0.1174151677455001</v>
       </c>
       <c r="T31">
-        <v>0.6850699024505632</v>
+        <v>0.6925734063109199</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>14.70585863468792</v>
+        <v>14.21566334686499</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09275361742185004</v>
+        <v>0.09248245165012965</v>
       </c>
       <c r="C32">
-        <v>3295.071862432383</v>
+        <v>3255.375776329169</v>
       </c>
       <c r="D32">
-        <v>4068.461862432383</v>
+        <v>4073.438776329169</v>
       </c>
       <c r="E32">
-        <v>660.09</v>
+        <v>704.763</v>
       </c>
       <c r="F32">
-        <v>1340.19</v>
+        <v>1384.863</v>
       </c>
       <c r="G32">
         <v>566.8</v>
@@ -3905,28 +3905,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M32">
-        <v>67.411557</v>
+        <v>69.6586089</v>
       </c>
       <c r="N32">
-        <v>890.8884430000001</v>
+        <v>888.6413911000001</v>
       </c>
       <c r="O32">
-        <v>267.2665329</v>
+        <v>266.59241733</v>
       </c>
       <c r="P32">
-        <v>623.6219101</v>
+        <v>622.0489737700001</v>
       </c>
       <c r="Q32">
-        <v>989.7219101000001</v>
+        <v>988.1489737700001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1174151677455001</v>
+        <v>0.1182135531161299</v>
       </c>
       <c r="T32">
-        <v>0.6925734063109199</v>
+        <v>0.700294403036794</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>14.21566334686499</v>
+        <v>13.75709356148225</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09248245165012965</v>
+        <v>0.09221128587840927</v>
       </c>
       <c r="C33">
-        <v>3255.375776329169</v>
+        <v>3215.691881570206</v>
       </c>
       <c r="D33">
-        <v>4073.438776329169</v>
+        <v>4078.427881570206</v>
       </c>
       <c r="E33">
-        <v>704.763</v>
+        <v>749.436</v>
       </c>
       <c r="F33">
-        <v>1384.863</v>
+        <v>1429.536</v>
       </c>
       <c r="G33">
         <v>566.8</v>
@@ -3987,28 +3987,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M33">
-        <v>69.6586089</v>
+        <v>71.90566079999999</v>
       </c>
       <c r="N33">
-        <v>888.6413911000001</v>
+        <v>886.3943392000001</v>
       </c>
       <c r="O33">
-        <v>266.59241733</v>
+        <v>265.91830176</v>
       </c>
       <c r="P33">
-        <v>622.0489737700001</v>
+        <v>620.47603744</v>
       </c>
       <c r="Q33">
-        <v>988.1489737700001</v>
+        <v>986.5760374400001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1182135531161299</v>
+        <v>0.1190354204094254</v>
       </c>
       <c r="T33">
-        <v>0.700294403036794</v>
+        <v>0.7082424879016646</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>13.75709356148225</v>
+        <v>13.32718438768593</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09221128587840927</v>
+        <v>0.09194012010668889</v>
       </c>
       <c r="C34">
-        <v>3215.691881570206</v>
+        <v>3176.020223005921</v>
       </c>
       <c r="D34">
-        <v>4078.427881570206</v>
+        <v>4083.429223005921</v>
       </c>
       <c r="E34">
-        <v>749.436</v>
+        <v>794.109</v>
       </c>
       <c r="F34">
-        <v>1429.536</v>
+        <v>1474.209</v>
       </c>
       <c r="G34">
         <v>566.8</v>
@@ -4069,28 +4069,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M34">
-        <v>71.90566079999999</v>
+        <v>74.1527127</v>
       </c>
       <c r="N34">
-        <v>886.3943392000001</v>
+        <v>884.1472873</v>
       </c>
       <c r="O34">
-        <v>265.91830176</v>
+        <v>265.24418619</v>
       </c>
       <c r="P34">
-        <v>620.47603744</v>
+        <v>618.9031011100001</v>
       </c>
       <c r="Q34">
-        <v>986.5760374400001</v>
+        <v>985.0031011100001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1190354204094254</v>
+        <v>0.1198818210547596</v>
       </c>
       <c r="T34">
-        <v>0.7082424879016646</v>
+        <v>0.7164278290311583</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>13.32718438768593</v>
+        <v>12.92333031533181</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09194012010668889</v>
+        <v>0.0920259543349685</v>
       </c>
       <c r="C35">
-        <v>3176.020223005921</v>
+        <v>3129.762782848782</v>
       </c>
       <c r="D35">
-        <v>4083.429223005921</v>
+        <v>4081.844782848782</v>
       </c>
       <c r="E35">
-        <v>794.109</v>
+        <v>838.782</v>
       </c>
       <c r="F35">
-        <v>1474.209</v>
+        <v>1518.882</v>
       </c>
       <c r="G35">
         <v>566.8</v>
@@ -4151,45 +4151,45 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M35">
-        <v>74.1527127</v>
+        <v>78.6780876</v>
       </c>
       <c r="N35">
-        <v>884.1472873</v>
+        <v>879.6219124</v>
       </c>
       <c r="O35">
-        <v>265.24418619</v>
+        <v>263.88657372</v>
       </c>
       <c r="P35">
-        <v>618.9031011100001</v>
+        <v>615.73533868</v>
       </c>
       <c r="Q35">
-        <v>985.0031011100001</v>
+        <v>981.8353386800001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1198818210547596</v>
+        <v>0.1207538702044977</v>
       </c>
       <c r="T35">
-        <v>0.7164278290311583</v>
+        <v>0.7248612108009395</v>
       </c>
       <c r="U35">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V35">
         <v>0.3</v>
       </c>
       <c r="W35">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y35">
-        <v>12.92333031533181</v>
+        <v>12.18001135045382</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0920259543349685</v>
+        <v>0.0917652885632481</v>
       </c>
       <c r="C36">
-        <v>3129.762782848782</v>
+        <v>3089.905299042608</v>
       </c>
       <c r="D36">
-        <v>4081.844782848782</v>
+        <v>4086.660299042608</v>
       </c>
       <c r="E36">
-        <v>838.782</v>
+        <v>883.4550000000003</v>
       </c>
       <c r="F36">
-        <v>1518.882</v>
+        <v>1563.555</v>
       </c>
       <c r="G36">
         <v>566.8</v>
@@ -4233,28 +4233,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M36">
-        <v>78.6780876</v>
+        <v>80.99214900000001</v>
       </c>
       <c r="N36">
-        <v>879.6219124</v>
+        <v>877.307851</v>
       </c>
       <c r="O36">
-        <v>263.88657372</v>
+        <v>263.1923553</v>
       </c>
       <c r="P36">
-        <v>615.73533868</v>
+        <v>614.1154957000001</v>
       </c>
       <c r="Q36">
-        <v>981.8353386800001</v>
+        <v>980.2154957000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1207538702044977</v>
+        <v>0.1216527516357663</v>
       </c>
       <c r="T36">
-        <v>0.7248612108009395</v>
+        <v>0.7335540812405601</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>12.18001135045382</v>
+        <v>11.83201102615514</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0917652885632481</v>
+        <v>0.09150462279152771</v>
       </c>
       <c r="C37">
-        <v>3089.905299042608</v>
+        <v>3050.059190772246</v>
       </c>
       <c r="D37">
-        <v>4086.660299042608</v>
+        <v>4091.487190772245</v>
       </c>
       <c r="E37">
-        <v>883.4550000000003</v>
+        <v>928.1280000000003</v>
       </c>
       <c r="F37">
-        <v>1563.555</v>
+        <v>1608.228</v>
       </c>
       <c r="G37">
         <v>566.8</v>
@@ -4315,28 +4315,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M37">
-        <v>80.99214900000001</v>
+        <v>83.30621040000001</v>
       </c>
       <c r="N37">
-        <v>877.307851</v>
+        <v>874.9937896</v>
       </c>
       <c r="O37">
-        <v>263.1923553</v>
+        <v>262.49813688</v>
       </c>
       <c r="P37">
-        <v>614.1154957000001</v>
+        <v>612.49565272</v>
       </c>
       <c r="Q37">
-        <v>980.2154957000001</v>
+        <v>978.59565272</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1216527516357663</v>
+        <v>0.1225797231117621</v>
       </c>
       <c r="T37">
-        <v>0.7335540812405601</v>
+        <v>0.7425186038814189</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.83201102615514</v>
+        <v>11.50334405320639</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09150462279152773</v>
+        <v>0.09124395701980735</v>
       </c>
       <c r="C38">
-        <v>3050.059190772246</v>
+        <v>3010.224498393442</v>
       </c>
       <c r="D38">
-        <v>4091.487190772245</v>
+        <v>4096.325498393441</v>
       </c>
       <c r="E38">
-        <v>928.128</v>
+        <v>972.801</v>
       </c>
       <c r="F38">
-        <v>1608.228</v>
+        <v>1652.901</v>
       </c>
       <c r="G38">
         <v>566.8</v>
@@ -4397,28 +4397,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M38">
-        <v>83.3062104</v>
+        <v>85.6202718</v>
       </c>
       <c r="N38">
-        <v>874.9937896000001</v>
+        <v>872.6797282000001</v>
       </c>
       <c r="O38">
-        <v>262.49813688</v>
+        <v>261.80391846</v>
       </c>
       <c r="P38">
-        <v>612.4956527200002</v>
+        <v>610.87580974</v>
       </c>
       <c r="Q38">
-        <v>978.5956527200002</v>
+        <v>976.97580974</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1225797231117621</v>
+        <v>0.1235361222536625</v>
       </c>
       <c r="T38">
-        <v>0.7425186038814189</v>
+        <v>0.7517677145426224</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>11.50334405320639</v>
+        <v>11.19244286257919</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09124395701980735</v>
+        <v>0.09098329124808695</v>
       </c>
       <c r="C39">
-        <v>3010.224498393442</v>
+        <v>2970.401262453057</v>
       </c>
       <c r="D39">
-        <v>4096.325498393441</v>
+        <v>4101.175262453057</v>
       </c>
       <c r="E39">
-        <v>972.801</v>
+        <v>1017.474</v>
       </c>
       <c r="F39">
-        <v>1652.901</v>
+        <v>1697.574</v>
       </c>
       <c r="G39">
         <v>566.8</v>
@@ -4479,28 +4479,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M39">
-        <v>85.6202718</v>
+        <v>87.9343332</v>
       </c>
       <c r="N39">
-        <v>872.6797282000001</v>
+        <v>870.3656668000001</v>
       </c>
       <c r="O39">
-        <v>261.80391846</v>
+        <v>261.10970004</v>
       </c>
       <c r="P39">
-        <v>610.87580974</v>
+        <v>609.2559667600001</v>
       </c>
       <c r="Q39">
-        <v>976.97580974</v>
+        <v>975.3559667600001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1235361222536625</v>
+        <v>0.1245233729807854</v>
       </c>
       <c r="T39">
-        <v>0.7517677145426224</v>
+        <v>0.7613151836122518</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>11.19244286257919</v>
+        <v>10.89790489251132</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09098329124808695</v>
+        <v>0.09072262547636657</v>
       </c>
       <c r="C40">
-        <v>2970.401262453057</v>
+        <v>2930.589523690202</v>
       </c>
       <c r="D40">
-        <v>4101.175262453057</v>
+        <v>4106.036523690202</v>
       </c>
       <c r="E40">
-        <v>1017.474</v>
+        <v>1062.147</v>
       </c>
       <c r="F40">
-        <v>1697.574</v>
+        <v>1742.247</v>
       </c>
       <c r="G40">
         <v>566.8</v>
@@ -4561,28 +4561,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M40">
-        <v>87.9343332</v>
+        <v>90.2483946</v>
       </c>
       <c r="N40">
-        <v>870.3656668000001</v>
+        <v>868.0516054000001</v>
       </c>
       <c r="O40">
-        <v>261.10970004</v>
+        <v>260.41548162</v>
       </c>
       <c r="P40">
-        <v>609.2559667600001</v>
+        <v>607.63612378</v>
       </c>
       <c r="Q40">
-        <v>975.3559667600001</v>
+        <v>973.7361237800001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1245233729807854</v>
+        <v>0.1255429925842075</v>
       </c>
       <c r="T40">
-        <v>0.7613151836122518</v>
+        <v>0.771175684454656</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.89790489251132</v>
+        <v>10.61847143372897</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09072262547636657</v>
+        <v>0.0904619597046462</v>
       </c>
       <c r="C41">
-        <v>2930.589523690202</v>
+        <v>2890.789323037367</v>
       </c>
       <c r="D41">
-        <v>4106.036523690202</v>
+        <v>4110.909323037367</v>
       </c>
       <c r="E41">
-        <v>1062.147</v>
+        <v>1106.82</v>
       </c>
       <c r="F41">
-        <v>1742.247</v>
+        <v>1786.92</v>
       </c>
       <c r="G41">
         <v>566.8</v>
@@ -4643,28 +4643,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M41">
-        <v>90.2483946</v>
+        <v>92.562456</v>
       </c>
       <c r="N41">
-        <v>868.0516054000001</v>
+        <v>865.7375440000001</v>
       </c>
       <c r="O41">
-        <v>260.41548162</v>
+        <v>259.7212632</v>
       </c>
       <c r="P41">
-        <v>607.63612378</v>
+        <v>606.0162808</v>
       </c>
       <c r="Q41">
-        <v>973.7361237800001</v>
+        <v>972.1162808</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1255429925842075</v>
+        <v>0.1265965995077437</v>
       </c>
       <c r="T41">
-        <v>0.771175684454656</v>
+        <v>0.7813648686584738</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>10.61847143372897</v>
+        <v>10.35300964788575</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0904619597046462</v>
+        <v>0.09020129393292581</v>
       </c>
       <c r="C42">
-        <v>2890.789323037367</v>
+        <v>2851.000701621585</v>
       </c>
       <c r="D42">
-        <v>4110.909323037367</v>
+        <v>4115.793701621585</v>
       </c>
       <c r="E42">
-        <v>1106.82</v>
+        <v>1151.493</v>
       </c>
       <c r="F42">
-        <v>1786.92</v>
+        <v>1831.593</v>
       </c>
       <c r="G42">
         <v>566.8</v>
@@ -4725,28 +4725,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M42">
-        <v>92.562456</v>
+        <v>94.87651740000001</v>
       </c>
       <c r="N42">
-        <v>865.7375440000001</v>
+        <v>863.4234826000001</v>
       </c>
       <c r="O42">
-        <v>259.7212632</v>
+        <v>259.02704478</v>
       </c>
       <c r="P42">
-        <v>606.0162808</v>
+        <v>604.3964378200001</v>
       </c>
       <c r="Q42">
-        <v>972.1162808</v>
+        <v>970.4964378200001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1265965995077437</v>
+        <v>0.1276859219202132</v>
       </c>
       <c r="T42">
-        <v>0.7813648686584738</v>
+        <v>0.791899448936997</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>10.35300964788575</v>
+        <v>10.10049721744951</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09020129393292581</v>
+        <v>0.08994062816120542</v>
       </c>
       <c r="C43">
-        <v>2851.000701621585</v>
+        <v>2811.223700765579</v>
       </c>
       <c r="D43">
-        <v>4115.793701621585</v>
+        <v>4120.68970076558</v>
       </c>
       <c r="E43">
-        <v>1151.493</v>
+        <v>1196.166</v>
       </c>
       <c r="F43">
-        <v>1831.593</v>
+        <v>1876.266</v>
       </c>
       <c r="G43">
         <v>566.8</v>
@@ -4807,28 +4807,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M43">
-        <v>94.87651740000001</v>
+        <v>97.19057880000001</v>
       </c>
       <c r="N43">
-        <v>863.4234826000001</v>
+        <v>861.1094212</v>
       </c>
       <c r="O43">
-        <v>259.02704478</v>
+        <v>258.33282636</v>
       </c>
       <c r="P43">
-        <v>604.3964378200001</v>
+        <v>602.77659484</v>
       </c>
       <c r="Q43">
-        <v>970.4964378200001</v>
+        <v>968.8765948400001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1276859219202132</v>
+        <v>0.1288128071744921</v>
       </c>
       <c r="T43">
-        <v>0.791899448936997</v>
+        <v>0.8027972906044349</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>10.10049721744951</v>
+        <v>9.860009188462616</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08994062816120542</v>
+        <v>0.09019166238948503</v>
       </c>
       <c r="C44">
-        <v>2811.22370076558</v>
+        <v>2761.83540071202</v>
       </c>
       <c r="D44">
-        <v>4120.68970076558</v>
+        <v>4115.97440071202</v>
       </c>
       <c r="E44">
-        <v>1196.166</v>
+        <v>1240.839</v>
       </c>
       <c r="F44">
-        <v>1876.266</v>
+        <v>1920.939</v>
       </c>
       <c r="G44">
         <v>566.8</v>
@@ -4889,45 +4889,45 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M44">
-        <v>97.1905788</v>
+        <v>102.7702365</v>
       </c>
       <c r="N44">
-        <v>861.1094212</v>
+        <v>855.5297635000001</v>
       </c>
       <c r="O44">
-        <v>258.33282636</v>
+        <v>256.65892905</v>
       </c>
       <c r="P44">
-        <v>602.77659484</v>
+        <v>598.8708344500001</v>
       </c>
       <c r="Q44">
-        <v>968.8765948400001</v>
+        <v>964.9708344500001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1288128071744921</v>
+        <v>0.1299792322622544</v>
       </c>
       <c r="T44">
-        <v>0.8027972906044348</v>
+        <v>0.8140775126812566</v>
       </c>
       <c r="U44">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V44">
         <v>0.3</v>
       </c>
       <c r="W44">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>9.860009188462618</v>
+        <v>9.324684194922526</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09019166238948503</v>
+        <v>0.08994289661776464</v>
       </c>
       <c r="C45">
-        <v>2761.83540071202</v>
+        <v>2721.835042851912</v>
       </c>
       <c r="D45">
-        <v>4115.97440071202</v>
+        <v>4120.647042851912</v>
       </c>
       <c r="E45">
-        <v>1240.839</v>
+        <v>1285.512</v>
       </c>
       <c r="F45">
-        <v>1920.939</v>
+        <v>1965.612</v>
       </c>
       <c r="G45">
         <v>566.8</v>
@@ -4971,28 +4971,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M45">
-        <v>102.7702365</v>
+        <v>105.160242</v>
       </c>
       <c r="N45">
-        <v>855.5297635000001</v>
+        <v>853.139758</v>
       </c>
       <c r="O45">
-        <v>256.65892905</v>
+        <v>255.9419274</v>
       </c>
       <c r="P45">
-        <v>598.8708344500001</v>
+        <v>597.1978306000001</v>
       </c>
       <c r="Q45">
-        <v>964.9708344500001</v>
+        <v>963.2978306000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1299792322622544</v>
+        <v>0.1311873153888654</v>
       </c>
       <c r="T45">
-        <v>0.8140775126812566</v>
+        <v>0.8257605998322505</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>9.324684194922526</v>
+        <v>9.112759554128832</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08994289661776464</v>
+        <v>0.08969413084604427</v>
       </c>
       <c r="C46">
-        <v>2721.835042851912</v>
+        <v>2681.845306243101</v>
       </c>
       <c r="D46">
-        <v>4120.647042851912</v>
+        <v>4125.3303062431</v>
       </c>
       <c r="E46">
-        <v>1285.512</v>
+        <v>1330.185</v>
       </c>
       <c r="F46">
-        <v>1965.612</v>
+        <v>2010.285</v>
       </c>
       <c r="G46">
         <v>566.8</v>
@@ -5053,28 +5053,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M46">
-        <v>105.160242</v>
+        <v>107.5502475</v>
       </c>
       <c r="N46">
-        <v>853.139758</v>
+        <v>850.7497525000001</v>
       </c>
       <c r="O46">
-        <v>255.9419274</v>
+        <v>255.22492575</v>
       </c>
       <c r="P46">
-        <v>597.1978306000001</v>
+        <v>595.5248267500001</v>
       </c>
       <c r="Q46">
-        <v>963.2978306000001</v>
+        <v>961.6248267500001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1311873153888654</v>
+        <v>0.1324393288109896</v>
       </c>
       <c r="T46">
-        <v>0.8257605998322505</v>
+        <v>0.837868526516008</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>9.112759554128832</v>
+        <v>8.910253786259304</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08969413084604427</v>
+        <v>0.08944536507432388</v>
       </c>
       <c r="C47">
-        <v>2681.845306243101</v>
+        <v>2641.866227141094</v>
       </c>
       <c r="D47">
-        <v>4125.3303062431</v>
+        <v>4130.024227141094</v>
       </c>
       <c r="E47">
-        <v>1330.185</v>
+        <v>1374.858</v>
       </c>
       <c r="F47">
-        <v>2010.285</v>
+        <v>2054.958</v>
       </c>
       <c r="G47">
         <v>566.8</v>
@@ -5135,28 +5135,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M47">
-        <v>107.5502475</v>
+        <v>109.940253</v>
       </c>
       <c r="N47">
-        <v>850.7497525000001</v>
+        <v>848.3597470000001</v>
       </c>
       <c r="O47">
-        <v>255.22492575</v>
+        <v>254.5079241</v>
       </c>
       <c r="P47">
-        <v>595.5248267500001</v>
+        <v>593.8518229000001</v>
       </c>
       <c r="Q47">
-        <v>961.6248267500001</v>
+        <v>959.9518229000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1324393288109896</v>
+        <v>0.1337377131005998</v>
       </c>
       <c r="T47">
-        <v>0.837868526516008</v>
+        <v>0.8504248949287933</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.910253786259304</v>
+        <v>8.716552616992796</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08944536507432388</v>
+        <v>0.08919659930260351</v>
       </c>
       <c r="C48">
-        <v>2641.866227141094</v>
+        <v>2601.897841966594</v>
       </c>
       <c r="D48">
-        <v>4130.024227141094</v>
+        <v>4134.728841966594</v>
       </c>
       <c r="E48">
-        <v>1374.858</v>
+        <v>1419.531</v>
       </c>
       <c r="F48">
-        <v>2054.958</v>
+        <v>2099.631</v>
       </c>
       <c r="G48">
         <v>566.8</v>
@@ -5217,28 +5217,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M48">
-        <v>109.940253</v>
+        <v>112.3302585</v>
       </c>
       <c r="N48">
-        <v>848.3597470000001</v>
+        <v>845.9697415000001</v>
       </c>
       <c r="O48">
-        <v>254.5079241</v>
+        <v>253.79092245</v>
       </c>
       <c r="P48">
-        <v>593.8518229000001</v>
+        <v>592.17881905</v>
       </c>
       <c r="Q48">
-        <v>959.9518229000001</v>
+        <v>958.27881905</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1337377131005998</v>
+        <v>0.1350850930237802</v>
       </c>
       <c r="T48">
-        <v>0.8504248949287933</v>
+        <v>0.8634550885647027</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.716552616992796</v>
+        <v>8.531094050673799</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08919659930260351</v>
+        <v>0.08894783353088312</v>
       </c>
       <c r="C49">
-        <v>2601.897841966594</v>
+        <v>2561.940187306449</v>
       </c>
       <c r="D49">
-        <v>4134.728841966594</v>
+        <v>4139.444187306449</v>
       </c>
       <c r="E49">
-        <v>1419.531</v>
+        <v>1464.204</v>
       </c>
       <c r="F49">
-        <v>2099.631</v>
+        <v>2144.304</v>
       </c>
       <c r="G49">
         <v>566.8</v>
@@ -5299,28 +5299,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M49">
-        <v>112.3302585</v>
+        <v>114.720264</v>
       </c>
       <c r="N49">
-        <v>845.9697415000001</v>
+        <v>843.579736</v>
       </c>
       <c r="O49">
-        <v>253.79092245</v>
+        <v>253.0739208</v>
       </c>
       <c r="P49">
-        <v>592.17881905</v>
+        <v>590.5058152</v>
       </c>
       <c r="Q49">
-        <v>958.27881905</v>
+        <v>956.6058152000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1350850930237802</v>
+        <v>0.1364842952516983</v>
       </c>
       <c r="T49">
-        <v>0.8634550885647027</v>
+        <v>0.8769864434943008</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.531094050673799</v>
+        <v>8.353362924618096</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08894783353088312</v>
+        <v>0.08869906775916273</v>
       </c>
       <c r="C50">
-        <v>2561.940187306449</v>
+        <v>2521.993299914591</v>
       </c>
       <c r="D50">
-        <v>4139.444187306449</v>
+        <v>4144.170299914591</v>
       </c>
       <c r="E50">
-        <v>1464.204</v>
+        <v>1508.877</v>
       </c>
       <c r="F50">
-        <v>2144.304</v>
+        <v>2188.977</v>
       </c>
       <c r="G50">
         <v>566.8</v>
@@ -5381,28 +5381,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M50">
-        <v>114.720264</v>
+        <v>117.1102695</v>
       </c>
       <c r="N50">
-        <v>843.579736</v>
+        <v>841.1897305000001</v>
       </c>
       <c r="O50">
-        <v>253.0739208</v>
+        <v>252.35691915</v>
       </c>
       <c r="P50">
-        <v>590.5058152</v>
+        <v>588.8328113500002</v>
       </c>
       <c r="Q50">
-        <v>956.6058152000001</v>
+        <v>954.9328113500002</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1364842952516983</v>
+        <v>0.137938368155221</v>
       </c>
       <c r="T50">
-        <v>0.8769864434943008</v>
+        <v>0.8910484397936871</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>8.353362924618096</v>
+        <v>8.182886130238135</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08869906775916273</v>
+        <v>0.08845030198744233</v>
       </c>
       <c r="C51">
-        <v>2521.993299914591</v>
+        <v>2482.057216712998</v>
       </c>
       <c r="D51">
-        <v>4144.170299914591</v>
+        <v>4148.907216712998</v>
       </c>
       <c r="E51">
-        <v>1508.877</v>
+        <v>1553.55</v>
       </c>
       <c r="F51">
-        <v>2188.977</v>
+        <v>2233.65</v>
       </c>
       <c r="G51">
         <v>566.8</v>
@@ -5463,28 +5463,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M51">
-        <v>117.1102695</v>
+        <v>119.500275</v>
       </c>
       <c r="N51">
-        <v>841.1897305000001</v>
+        <v>838.7997250000001</v>
       </c>
       <c r="O51">
-        <v>252.35691915</v>
+        <v>251.6399175</v>
       </c>
       <c r="P51">
-        <v>588.8328113500002</v>
+        <v>587.1598075000001</v>
       </c>
       <c r="Q51">
-        <v>954.9328113500002</v>
+        <v>953.2598075000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.137938368155221</v>
+        <v>0.1394506039748847</v>
       </c>
       <c r="T51">
-        <v>0.8910484397936871</v>
+        <v>0.905672915945049</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>8.182886130238135</v>
+        <v>8.019228407633372</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08845030198744233</v>
+        <v>0.08820153621572197</v>
       </c>
       <c r="C52">
-        <v>2482.057216712998</v>
+        <v>2442.131974792651</v>
       </c>
       <c r="D52">
-        <v>4148.907216712998</v>
+        <v>4153.654974792651</v>
       </c>
       <c r="E52">
-        <v>1553.55</v>
+        <v>1598.223</v>
       </c>
       <c r="F52">
-        <v>2233.65</v>
+        <v>2278.323</v>
       </c>
       <c r="G52">
         <v>566.8</v>
@@ -5545,28 +5545,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M52">
-        <v>119.500275</v>
+        <v>121.8902805</v>
       </c>
       <c r="N52">
-        <v>838.7997250000001</v>
+        <v>836.4097195000001</v>
       </c>
       <c r="O52">
-        <v>251.6399175</v>
+        <v>250.92291585</v>
       </c>
       <c r="P52">
-        <v>587.1598075000001</v>
+        <v>585.4868036500001</v>
       </c>
       <c r="Q52">
-        <v>953.2598075000001</v>
+        <v>951.5868036500001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1394506039748847</v>
+        <v>0.141024563705555</v>
       </c>
       <c r="T52">
-        <v>0.905672915945049</v>
+        <v>0.920894309490344</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>8.019228407633372</v>
+        <v>7.861988634934677</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08820153621572197</v>
+        <v>0.08795277044400157</v>
       </c>
       <c r="C53">
-        <v>2442.131974792651</v>
+        <v>2402.217611414507</v>
       </c>
       <c r="D53">
-        <v>4153.654974792651</v>
+        <v>4158.413611414507</v>
       </c>
       <c r="E53">
-        <v>1598.223</v>
+        <v>1642.896</v>
       </c>
       <c r="F53">
-        <v>2278.323</v>
+        <v>2322.996</v>
       </c>
       <c r="G53">
         <v>566.8</v>
@@ -5627,28 +5627,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M53">
-        <v>121.8902805</v>
+        <v>124.280286</v>
       </c>
       <c r="N53">
-        <v>836.4097195000001</v>
+        <v>834.019714</v>
       </c>
       <c r="O53">
-        <v>250.92291585</v>
+        <v>250.2059142</v>
       </c>
       <c r="P53">
-        <v>585.4868036500001</v>
+        <v>583.8137998</v>
       </c>
       <c r="Q53">
-        <v>951.5868036500001</v>
+        <v>949.9137998</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.141024563705555</v>
+        <v>0.14266410509167</v>
       </c>
       <c r="T53">
-        <v>0.920894309490344</v>
+        <v>0.9367499277666929</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.861988634934677</v>
+        <v>7.710796545801319</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08795277044400157</v>
+        <v>0.08800080467228119</v>
       </c>
       <c r="C54">
-        <v>2402.217611414507</v>
+        <v>2356.624916173382</v>
       </c>
       <c r="D54">
-        <v>4158.413611414507</v>
+        <v>4157.493916173382</v>
       </c>
       <c r="E54">
-        <v>1642.896</v>
+        <v>1687.569</v>
       </c>
       <c r="F54">
-        <v>2322.996</v>
+        <v>2367.669</v>
       </c>
       <c r="G54">
         <v>566.8</v>
@@ -5709,45 +5709,45 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M54">
-        <v>124.280286</v>
+        <v>128.5644267</v>
       </c>
       <c r="N54">
-        <v>834.019714</v>
+        <v>829.7355733000001</v>
       </c>
       <c r="O54">
-        <v>250.2059142</v>
+        <v>248.92067199</v>
       </c>
       <c r="P54">
-        <v>583.8137998</v>
+        <v>580.8149013100001</v>
       </c>
       <c r="Q54">
-        <v>949.9137998</v>
+        <v>946.9149013100001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.14266410509167</v>
+        <v>0.1443734141963429</v>
       </c>
       <c r="T54">
-        <v>0.9367499277666929</v>
+        <v>0.9532802532037374</v>
       </c>
       <c r="U54">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V54">
         <v>0.3</v>
       </c>
       <c r="W54">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y54">
-        <v>7.710796545801319</v>
+        <v>7.453850373681944</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08800080467228119</v>
+        <v>0.08775763890056079</v>
       </c>
       <c r="C55">
-        <v>2356.624916173382</v>
+        <v>2316.611917254871</v>
       </c>
       <c r="D55">
-        <v>4157.493916173382</v>
+        <v>4162.153917254871</v>
       </c>
       <c r="E55">
-        <v>1687.569</v>
+        <v>1732.242</v>
       </c>
       <c r="F55">
-        <v>2367.669</v>
+        <v>2412.342</v>
       </c>
       <c r="G55">
         <v>566.8</v>
@@ -5791,28 +5791,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M55">
-        <v>128.5644267</v>
+        <v>130.9901706</v>
       </c>
       <c r="N55">
-        <v>829.7355733000001</v>
+        <v>827.3098294000001</v>
       </c>
       <c r="O55">
-        <v>248.92067199</v>
+        <v>248.19294882</v>
       </c>
       <c r="P55">
-        <v>580.8149013100001</v>
+        <v>579.11688058</v>
       </c>
       <c r="Q55">
-        <v>946.9149013100001</v>
+        <v>945.2168805800001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1443734141963429</v>
+        <v>0.1461570410881756</v>
       </c>
       <c r="T55">
-        <v>0.9532802532037374</v>
+        <v>0.9705292884423926</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.453850373681944</v>
+        <v>7.31581610750265</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08775763890056079</v>
+        <v>0.08751447312884042</v>
       </c>
       <c r="C56">
-        <v>2316.611917254871</v>
+        <v>2276.609376549003</v>
       </c>
       <c r="D56">
-        <v>4162.153917254871</v>
+        <v>4166.824376549003</v>
       </c>
       <c r="E56">
-        <v>1732.242</v>
+        <v>1776.915</v>
       </c>
       <c r="F56">
-        <v>2412.342</v>
+        <v>2457.015</v>
       </c>
       <c r="G56">
         <v>566.8</v>
@@ -5873,28 +5873,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M56">
-        <v>130.9901706</v>
+        <v>133.4159145</v>
       </c>
       <c r="N56">
-        <v>827.3098294000001</v>
+        <v>824.8840855000001</v>
       </c>
       <c r="O56">
-        <v>248.19294882</v>
+        <v>247.46522565</v>
       </c>
       <c r="P56">
-        <v>579.11688058</v>
+        <v>577.4188598500001</v>
       </c>
       <c r="Q56">
-        <v>945.2168805800001</v>
+        <v>943.5188598500001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1461570410881756</v>
+        <v>0.148019940286312</v>
       </c>
       <c r="T56">
-        <v>0.9705292884423926</v>
+        <v>0.9885449474694327</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>7.31581610750265</v>
+        <v>7.182801269184419</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08751447312884042</v>
+        <v>0.08727130735712003</v>
       </c>
       <c r="C57">
-        <v>2276.609376549003</v>
+        <v>2236.617329301613</v>
       </c>
       <c r="D57">
-        <v>4166.824376549003</v>
+        <v>4171.505329301614</v>
       </c>
       <c r="E57">
-        <v>1776.915</v>
+        <v>1821.588000000001</v>
       </c>
       <c r="F57">
-        <v>2457.015</v>
+        <v>2501.688000000001</v>
       </c>
       <c r="G57">
         <v>566.8</v>
@@ -5955,28 +5955,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M57">
-        <v>133.4159145</v>
+        <v>135.8416584</v>
       </c>
       <c r="N57">
-        <v>824.8840855000001</v>
+        <v>822.4583416</v>
       </c>
       <c r="O57">
-        <v>247.46522565</v>
+        <v>246.73750248</v>
       </c>
       <c r="P57">
-        <v>577.4188598500001</v>
+        <v>575.7208391200001</v>
       </c>
       <c r="Q57">
-        <v>943.5188598500001</v>
+        <v>941.8208391200001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.148019940286312</v>
+        <v>0.1499675167207274</v>
       </c>
       <c r="T57">
-        <v>0.9885449474694327</v>
+        <v>1.007379500088611</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>7.182801269184419</v>
+        <v>7.054536960806125</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08727130735712003</v>
+        <v>0.08702814158539965</v>
       </c>
       <c r="C58">
-        <v>2236.617329301613</v>
+        <v>2196.635810917091</v>
       </c>
       <c r="D58">
-        <v>4171.505329301614</v>
+        <v>4176.196810917091</v>
       </c>
       <c r="E58">
-        <v>1821.588000000001</v>
+        <v>1866.261</v>
       </c>
       <c r="F58">
-        <v>2501.688000000001</v>
+        <v>2546.361</v>
       </c>
       <c r="G58">
         <v>566.8</v>
@@ -6037,28 +6037,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M58">
-        <v>135.8416584</v>
+        <v>138.2674023</v>
       </c>
       <c r="N58">
-        <v>822.4583416</v>
+        <v>820.0325977</v>
       </c>
       <c r="O58">
-        <v>246.73750248</v>
+        <v>246.00977931</v>
       </c>
       <c r="P58">
-        <v>575.7208391200001</v>
+        <v>574.02281839</v>
       </c>
       <c r="Q58">
-        <v>941.8208391200001</v>
+        <v>940.12281839</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1499675167207274</v>
+        <v>0.1520056781055806</v>
       </c>
       <c r="T58">
-        <v>1.007379500088611</v>
+        <v>1.027090078411006</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>7.054536960806125</v>
+        <v>6.930773154476194</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08702814158539965</v>
+        <v>0.08678497581367926</v>
       </c>
       <c r="C59">
-        <v>2196.635810917091</v>
+        <v>2156.664856959276</v>
       </c>
       <c r="D59">
-        <v>4176.196810917091</v>
+        <v>4180.898856959277</v>
       </c>
       <c r="E59">
-        <v>1866.261</v>
+        <v>1910.934000000001</v>
       </c>
       <c r="F59">
-        <v>2546.361</v>
+        <v>2591.034000000001</v>
       </c>
       <c r="G59">
         <v>566.8</v>
@@ -6119,28 +6119,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M59">
-        <v>138.2674023</v>
+        <v>140.6931462</v>
       </c>
       <c r="N59">
-        <v>820.0325977</v>
+        <v>817.6068538000001</v>
       </c>
       <c r="O59">
-        <v>246.00977931</v>
+        <v>245.28205614</v>
       </c>
       <c r="P59">
-        <v>574.02281839</v>
+        <v>572.3247976600001</v>
       </c>
       <c r="Q59">
-        <v>940.12281839</v>
+        <v>938.4247976600001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1520056781055806</v>
+        <v>0.1541408947944745</v>
       </c>
       <c r="T59">
-        <v>1.027090078411006</v>
+        <v>1.047739255701135</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.930773154476194</v>
+        <v>6.811277065605914</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08678497581367928</v>
+        <v>0.08654181004195888</v>
       </c>
       <c r="C60">
-        <v>2156.664856959277</v>
+        <v>2116.704503152357</v>
       </c>
       <c r="D60">
-        <v>4180.898856959277</v>
+        <v>4185.611503152357</v>
       </c>
       <c r="E60">
-        <v>1910.934</v>
+        <v>1955.607</v>
       </c>
       <c r="F60">
-        <v>2591.034</v>
+        <v>2635.707</v>
       </c>
       <c r="G60">
         <v>566.8</v>
@@ -6201,28 +6201,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M60">
-        <v>140.6931462</v>
+        <v>143.1188901</v>
       </c>
       <c r="N60">
-        <v>817.6068538000001</v>
+        <v>815.1811099000001</v>
       </c>
       <c r="O60">
-        <v>245.28205614</v>
+        <v>244.55433297</v>
       </c>
       <c r="P60">
-        <v>572.3247976600001</v>
+        <v>570.6267769300001</v>
       </c>
       <c r="Q60">
-        <v>938.4247976600001</v>
+        <v>936.7267769300001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1541408947944744</v>
+        <v>0.1563802683950216</v>
       </c>
       <c r="T60">
-        <v>1.047739255701135</v>
+        <v>1.069395709932246</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.811277065605916</v>
+        <v>6.695831691612596</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08654181004195888</v>
+        <v>0.08629864427023849</v>
       </c>
       <c r="C61">
-        <v>2116.704503152357</v>
+        <v>2076.754785381772</v>
       </c>
       <c r="D61">
-        <v>4185.611503152357</v>
+        <v>4190.334785381772</v>
       </c>
       <c r="E61">
-        <v>1955.607</v>
+        <v>2000.28</v>
       </c>
       <c r="F61">
-        <v>2635.707</v>
+        <v>2680.38</v>
       </c>
       <c r="G61">
         <v>566.8</v>
@@ -6283,28 +6283,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M61">
-        <v>143.1188901</v>
+        <v>145.544634</v>
       </c>
       <c r="N61">
-        <v>815.1811099000001</v>
+        <v>812.7553660000001</v>
       </c>
       <c r="O61">
-        <v>244.55433297</v>
+        <v>243.8266098</v>
       </c>
       <c r="P61">
-        <v>570.6267769300001</v>
+        <v>568.9287562000001</v>
       </c>
       <c r="Q61">
-        <v>936.7267769300001</v>
+        <v>935.0287562000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1563802683950216</v>
+        <v>0.1587316106755962</v>
       </c>
       <c r="T61">
-        <v>1.069395709932246</v>
+        <v>1.092134986874912</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.695831691612596</v>
+        <v>6.584234496752385</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08629864427023849</v>
+        <v>0.08605547849851811</v>
       </c>
       <c r="C62">
-        <v>2076.754785381772</v>
+        <v>2036.815739695127</v>
       </c>
       <c r="D62">
-        <v>4190.334785381772</v>
+        <v>4195.068739695127</v>
       </c>
       <c r="E62">
-        <v>2000.28</v>
+        <v>2044.953</v>
       </c>
       <c r="F62">
-        <v>2680.38</v>
+        <v>2725.053</v>
       </c>
       <c r="G62">
         <v>566.8</v>
@@ -6365,28 +6365,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M62">
-        <v>145.544634</v>
+        <v>147.9703779</v>
       </c>
       <c r="N62">
-        <v>812.7553660000001</v>
+        <v>810.3296221000001</v>
       </c>
       <c r="O62">
-        <v>243.8266098</v>
+        <v>243.09888663</v>
       </c>
       <c r="P62">
-        <v>568.9287562000001</v>
+        <v>567.23073547</v>
       </c>
       <c r="Q62">
-        <v>935.0287562000001</v>
+        <v>933.33073547</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1587316106755962</v>
+        <v>0.1612035346115849</v>
       </c>
       <c r="T62">
-        <v>1.092134986874912</v>
+        <v>1.116040380583869</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.584234496752385</v>
+        <v>6.476296226313822</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08605547849851811</v>
+        <v>0.08581231272679773</v>
       </c>
       <c r="C63">
-        <v>2036.815739695127</v>
+        <v>1996.887402303108</v>
       </c>
       <c r="D63">
-        <v>4195.068739695127</v>
+        <v>4199.813402303108</v>
       </c>
       <c r="E63">
-        <v>2044.953</v>
+        <v>2089.626</v>
       </c>
       <c r="F63">
-        <v>2725.053</v>
+        <v>2769.726</v>
       </c>
       <c r="G63">
         <v>566.8</v>
@@ -6447,28 +6447,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M63">
-        <v>147.9703779</v>
+        <v>150.3961218</v>
       </c>
       <c r="N63">
-        <v>810.3296221000001</v>
+        <v>807.9038782</v>
       </c>
       <c r="O63">
-        <v>243.09888663</v>
+        <v>242.37116346</v>
       </c>
       <c r="P63">
-        <v>567.23073547</v>
+        <v>565.5327147400001</v>
       </c>
       <c r="Q63">
-        <v>933.33073547</v>
+        <v>931.6327147400001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1612035346115849</v>
+        <v>0.1638055598073624</v>
       </c>
       <c r="T63">
-        <v>1.116040380583869</v>
+        <v>1.141203952909086</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>6.476296226313822</v>
+        <v>6.371839835566823</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08581231272679773</v>
+        <v>0.08556914695507734</v>
       </c>
       <c r="C64">
-        <v>1996.887402303108</v>
+        <v>1956.969809580403</v>
       </c>
       <c r="D64">
-        <v>4199.813402303108</v>
+        <v>4204.568809580403</v>
       </c>
       <c r="E64">
-        <v>2089.626</v>
+        <v>2134.299</v>
       </c>
       <c r="F64">
-        <v>2769.726</v>
+        <v>2814.399</v>
       </c>
       <c r="G64">
         <v>566.8</v>
@@ -6529,28 +6529,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M64">
-        <v>150.3961218</v>
+        <v>152.8218657</v>
       </c>
       <c r="N64">
-        <v>807.9038782</v>
+        <v>805.4781343000001</v>
       </c>
       <c r="O64">
-        <v>242.37116346</v>
+        <v>241.64344029</v>
       </c>
       <c r="P64">
-        <v>565.5327147400001</v>
+        <v>563.83469401</v>
       </c>
       <c r="Q64">
-        <v>931.6327147400001</v>
+        <v>929.93469401</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1638055598073624</v>
+        <v>0.1665482350137225</v>
       </c>
       <c r="T64">
-        <v>1.141203952909086</v>
+        <v>1.167727718332965</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>6.371839835566823</v>
+        <v>6.270699520716557</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08556914695507734</v>
+        <v>0.08532598118335696</v>
       </c>
       <c r="C65">
-        <v>1956.969809580403</v>
+        <v>1917.062998066634</v>
       </c>
       <c r="D65">
-        <v>4204.568809580403</v>
+        <v>4209.334998066634</v>
       </c>
       <c r="E65">
-        <v>2134.299</v>
+        <v>2178.972</v>
       </c>
       <c r="F65">
-        <v>2814.399</v>
+        <v>2859.072</v>
       </c>
       <c r="G65">
         <v>566.8</v>
@@ -6611,28 +6611,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M65">
-        <v>152.8218657</v>
+        <v>155.2476096</v>
       </c>
       <c r="N65">
-        <v>805.4781343000001</v>
+        <v>803.0523904</v>
       </c>
       <c r="O65">
-        <v>241.64344029</v>
+        <v>240.91571712</v>
       </c>
       <c r="P65">
-        <v>563.83469401</v>
+        <v>562.13667328</v>
       </c>
       <c r="Q65">
-        <v>929.93469401</v>
+        <v>928.23667328</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1665482350137225</v>
+        <v>0.1694432810648805</v>
       </c>
       <c r="T65">
-        <v>1.167727718332965</v>
+        <v>1.195725026280392</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>6.270699520716557</v>
+        <v>6.17271984070536</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08532598118335696</v>
+        <v>0.08553781541163658</v>
       </c>
       <c r="C66">
-        <v>1917.062998066634</v>
+        <v>1868.237319937916</v>
       </c>
       <c r="D66">
-        <v>4209.334998066634</v>
+        <v>4205.182319937916</v>
       </c>
       <c r="E66">
-        <v>2178.972</v>
+        <v>2223.645</v>
       </c>
       <c r="F66">
-        <v>2859.072</v>
+        <v>2903.745</v>
       </c>
       <c r="G66">
         <v>566.8</v>
@@ -6693,45 +6693,45 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M66">
-        <v>155.2476096</v>
+        <v>160.5770985</v>
       </c>
       <c r="N66">
-        <v>803.0523904</v>
+        <v>797.7229015</v>
       </c>
       <c r="O66">
-        <v>240.91571712</v>
+        <v>239.31687045</v>
       </c>
       <c r="P66">
-        <v>562.13667328</v>
+        <v>558.40603105</v>
       </c>
       <c r="Q66">
-        <v>928.23667328</v>
+        <v>924.50603105</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1694432810648805</v>
+        <v>0.1725037583189616</v>
       </c>
       <c r="T66">
-        <v>1.195725026280392</v>
+        <v>1.225322180396243</v>
       </c>
       <c r="U66">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V66">
         <v>0.3</v>
       </c>
       <c r="W66">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y66">
-        <v>6.17271984070536</v>
+        <v>5.967849767817294</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08553781541163658</v>
+        <v>0.0853016496399162</v>
       </c>
       <c r="C67">
-        <v>1868.237319937916</v>
+        <v>1828.194505040058</v>
       </c>
       <c r="D67">
-        <v>4205.182319937916</v>
+        <v>4209.812505040058</v>
       </c>
       <c r="E67">
-        <v>2223.645</v>
+        <v>2268.318</v>
       </c>
       <c r="F67">
-        <v>2903.745</v>
+        <v>2948.418</v>
       </c>
       <c r="G67">
         <v>566.8</v>
@@ -6775,28 +6775,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M67">
-        <v>160.5770985</v>
+        <v>163.0475154</v>
       </c>
       <c r="N67">
-        <v>797.7229015</v>
+        <v>795.2524846000001</v>
       </c>
       <c r="O67">
-        <v>239.31687045</v>
+        <v>238.57574538</v>
       </c>
       <c r="P67">
-        <v>558.40603105</v>
+        <v>556.6767392200001</v>
       </c>
       <c r="Q67">
-        <v>924.50603105</v>
+        <v>922.7767392200001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1725037583189616</v>
+        <v>0.1757442636468123</v>
       </c>
       <c r="T67">
-        <v>1.225322180396243</v>
+        <v>1.256660343577732</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.967849767817294</v>
+        <v>5.877427801638246</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0853016496399162</v>
+        <v>0.0850654838681958</v>
       </c>
       <c r="C68">
-        <v>1828.194505040058</v>
+        <v>1788.161897664158</v>
       </c>
       <c r="D68">
-        <v>4209.812505040058</v>
+        <v>4214.452897664159</v>
       </c>
       <c r="E68">
-        <v>2268.318</v>
+        <v>2312.991</v>
       </c>
       <c r="F68">
-        <v>2948.418</v>
+        <v>2993.091</v>
       </c>
       <c r="G68">
         <v>566.8</v>
@@ -6857,28 +6857,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M68">
-        <v>163.0475154</v>
+        <v>165.5179323</v>
       </c>
       <c r="N68">
-        <v>795.2524846000001</v>
+        <v>792.7820677000001</v>
       </c>
       <c r="O68">
-        <v>238.57574538</v>
+        <v>237.83462031</v>
       </c>
       <c r="P68">
-        <v>556.6767392200001</v>
+        <v>554.9474473900001</v>
       </c>
       <c r="Q68">
-        <v>922.7767392200001</v>
+        <v>921.0474473900001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1757442636468123</v>
+        <v>0.179181163236957</v>
       </c>
       <c r="T68">
-        <v>1.256660343577732</v>
+        <v>1.289897789376282</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.877427801638246</v>
+        <v>5.78970499862872</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0850654838681958</v>
+        <v>0.08482931809647543</v>
       </c>
       <c r="C69">
-        <v>1788.161897664158</v>
+        <v>1748.139531602112</v>
       </c>
       <c r="D69">
-        <v>4214.452897664159</v>
+        <v>4219.103531602112</v>
       </c>
       <c r="E69">
-        <v>2312.991</v>
+        <v>2357.664</v>
       </c>
       <c r="F69">
-        <v>2993.091</v>
+        <v>3037.764</v>
       </c>
       <c r="G69">
         <v>566.8</v>
@@ -6939,28 +6939,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M69">
-        <v>165.5179323</v>
+        <v>167.9883492</v>
       </c>
       <c r="N69">
-        <v>792.7820677000001</v>
+        <v>790.3116508000001</v>
       </c>
       <c r="O69">
-        <v>237.83462031</v>
+        <v>237.09349524</v>
       </c>
       <c r="P69">
-        <v>554.9474473900001</v>
+        <v>553.21815556</v>
       </c>
       <c r="Q69">
-        <v>921.0474473900001</v>
+        <v>919.31815556</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.179181163236957</v>
+        <v>0.1828328690514857</v>
       </c>
       <c r="T69">
-        <v>1.289897789376282</v>
+        <v>1.325212575537241</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.78970499862872</v>
+        <v>5.70456227806065</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08482931809647543</v>
+        <v>0.08459315232475503</v>
       </c>
       <c r="C70">
-        <v>1748.139531602112</v>
+        <v>1708.127440795135</v>
       </c>
       <c r="D70">
-        <v>4219.103531602112</v>
+        <v>4223.764440795136</v>
       </c>
       <c r="E70">
-        <v>2357.664</v>
+        <v>2402.337</v>
       </c>
       <c r="F70">
-        <v>3037.764</v>
+        <v>3082.437</v>
       </c>
       <c r="G70">
         <v>566.8</v>
@@ -7021,28 +7021,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M70">
-        <v>167.9883492</v>
+        <v>170.4587661</v>
       </c>
       <c r="N70">
-        <v>790.3116508000001</v>
+        <v>787.8412339</v>
       </c>
       <c r="O70">
-        <v>237.09349524</v>
+        <v>236.35237017</v>
       </c>
       <c r="P70">
-        <v>553.21815556</v>
+        <v>551.48886373</v>
       </c>
       <c r="Q70">
-        <v>919.31815556</v>
+        <v>917.5888637300001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1828328690514857</v>
+        <v>0.1867201687895324</v>
       </c>
       <c r="T70">
-        <v>1.325212575537241</v>
+        <v>1.362805734998907</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.70456227806065</v>
+        <v>5.621887462436582</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08459315232475503</v>
+        <v>0.08435698655303464</v>
       </c>
       <c r="C71">
-        <v>1708.127440795135</v>
+        <v>1668.125659334591</v>
       </c>
       <c r="D71">
-        <v>4223.764440795136</v>
+        <v>4228.435659334591</v>
       </c>
       <c r="E71">
-        <v>2402.337</v>
+        <v>2447.010000000001</v>
       </c>
       <c r="F71">
-        <v>3082.437</v>
+        <v>3127.110000000001</v>
       </c>
       <c r="G71">
         <v>566.8</v>
@@ -7103,28 +7103,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M71">
-        <v>170.4587661</v>
+        <v>172.9291830000001</v>
       </c>
       <c r="N71">
-        <v>787.8412339</v>
+        <v>785.370817</v>
       </c>
       <c r="O71">
-        <v>236.35237017</v>
+        <v>235.6112451</v>
       </c>
       <c r="P71">
-        <v>551.48886373</v>
+        <v>549.7595719</v>
       </c>
       <c r="Q71">
-        <v>917.5888637300001</v>
+        <v>915.8595719</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1867201687895324</v>
+        <v>0.1908666218434489</v>
       </c>
       <c r="T71">
-        <v>1.362805734998907</v>
+        <v>1.402905105091351</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.621887462436582</v>
+        <v>5.541574784401773</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08435698655303464</v>
+        <v>0.08412082078131428</v>
       </c>
       <c r="C72">
-        <v>1668.125659334591</v>
+        <v>1628.134221462818</v>
       </c>
       <c r="D72">
-        <v>4228.435659334591</v>
+        <v>4233.117221462819</v>
       </c>
       <c r="E72">
-        <v>2447.010000000001</v>
+        <v>2491.683</v>
       </c>
       <c r="F72">
-        <v>3127.110000000001</v>
+        <v>3171.783</v>
       </c>
       <c r="G72">
         <v>566.8</v>
@@ -7185,28 +7185,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M72">
-        <v>172.9291830000001</v>
+        <v>175.3995999</v>
       </c>
       <c r="N72">
-        <v>785.370817</v>
+        <v>782.9004001000001</v>
       </c>
       <c r="O72">
-        <v>235.6112451</v>
+        <v>234.87012003</v>
       </c>
       <c r="P72">
-        <v>549.7595719</v>
+        <v>548.0302800700001</v>
       </c>
       <c r="Q72">
-        <v>915.8595719</v>
+        <v>914.1302800700001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1908666218434489</v>
+        <v>0.1952990371769458</v>
       </c>
       <c r="T72">
-        <v>1.402905105091351</v>
+        <v>1.445769948983273</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.541574784401773</v>
+        <v>5.463524435325692</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08412082078131428</v>
+        <v>0.08388465500959388</v>
       </c>
       <c r="C73">
-        <v>1628.134221462819</v>
+        <v>1588.153161573977</v>
       </c>
       <c r="D73">
-        <v>4233.117221462819</v>
+        <v>4237.809161573977</v>
       </c>
       <c r="E73">
-        <v>2491.683</v>
+        <v>2536.356</v>
       </c>
       <c r="F73">
-        <v>3171.783</v>
+        <v>3216.456</v>
       </c>
       <c r="G73">
         <v>566.8</v>
@@ -7267,28 +7267,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M73">
-        <v>175.3995999</v>
+        <v>177.8700168</v>
       </c>
       <c r="N73">
-        <v>782.9004001000001</v>
+        <v>780.4299832</v>
       </c>
       <c r="O73">
-        <v>234.87012003</v>
+        <v>234.12899496</v>
       </c>
       <c r="P73">
-        <v>548.0302800700001</v>
+        <v>546.30098824</v>
       </c>
       <c r="Q73">
-        <v>914.1302800700001</v>
+        <v>912.4009882400001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1952990371769457</v>
+        <v>0.2000480536056924</v>
       </c>
       <c r="T73">
-        <v>1.445769948983273</v>
+        <v>1.491696567438904</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.463524435325693</v>
+        <v>5.387642151501725</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08388465500959388</v>
+        <v>0.08364848923787349</v>
       </c>
       <c r="C74">
-        <v>1588.153161573977</v>
+        <v>1548.182514214879</v>
       </c>
       <c r="D74">
-        <v>4237.809161573977</v>
+        <v>4242.511514214879</v>
       </c>
       <c r="E74">
-        <v>2536.356</v>
+        <v>2581.029</v>
       </c>
       <c r="F74">
-        <v>3216.456</v>
+        <v>3261.129</v>
       </c>
       <c r="G74">
         <v>566.8</v>
@@ -7349,28 +7349,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M74">
-        <v>177.8700168</v>
+        <v>180.3404337</v>
       </c>
       <c r="N74">
-        <v>780.4299832</v>
+        <v>777.9595663</v>
       </c>
       <c r="O74">
-        <v>234.12899496</v>
+        <v>233.38786989</v>
       </c>
       <c r="P74">
-        <v>546.30098824</v>
+        <v>544.57169641</v>
       </c>
       <c r="Q74">
-        <v>912.4009882400001</v>
+        <v>910.67169641</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2000480536056924</v>
+        <v>0.2051488490291611</v>
       </c>
       <c r="T74">
-        <v>1.491696567438904</v>
+        <v>1.54102515763199</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.387642151501725</v>
+        <v>5.313838834357866</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08364848923787349</v>
+        <v>0.0834123234661531</v>
       </c>
       <c r="C75">
-        <v>1548.182514214879</v>
+        <v>1508.222314085846</v>
       </c>
       <c r="D75">
-        <v>4242.511514214879</v>
+        <v>4247.224314085846</v>
       </c>
       <c r="E75">
-        <v>2581.029</v>
+        <v>2625.702</v>
       </c>
       <c r="F75">
-        <v>3261.129</v>
+        <v>3305.802</v>
       </c>
       <c r="G75">
         <v>566.8</v>
@@ -7431,28 +7431,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M75">
-        <v>180.3404337</v>
+        <v>182.8108506</v>
       </c>
       <c r="N75">
-        <v>777.9595663</v>
+        <v>775.4891494000001</v>
       </c>
       <c r="O75">
-        <v>233.38786989</v>
+        <v>232.64674482</v>
       </c>
       <c r="P75">
-        <v>544.57169641</v>
+        <v>542.8424045800001</v>
       </c>
       <c r="Q75">
-        <v>910.67169641</v>
+        <v>908.9424045800001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2051488490291611</v>
+        <v>0.2106420133313581</v>
       </c>
       <c r="T75">
-        <v>1.54102515763199</v>
+        <v>1.594148254763005</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.313838834357866</v>
+        <v>5.242030201461138</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0834123234661531</v>
+        <v>0.08317615769443273</v>
       </c>
       <c r="C76">
-        <v>1508.222314085846</v>
+        <v>1468.272596041555</v>
       </c>
       <c r="D76">
-        <v>4247.224314085846</v>
+        <v>4251.947596041555</v>
       </c>
       <c r="E76">
-        <v>2625.702</v>
+        <v>2670.375</v>
       </c>
       <c r="F76">
-        <v>3305.802</v>
+        <v>3350.475</v>
       </c>
       <c r="G76">
         <v>566.8</v>
@@ -7513,28 +7513,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M76">
-        <v>182.8108506</v>
+        <v>185.2812675</v>
       </c>
       <c r="N76">
-        <v>775.4891494000001</v>
+        <v>773.0187325000001</v>
       </c>
       <c r="O76">
-        <v>232.64674482</v>
+        <v>231.90561975</v>
       </c>
       <c r="P76">
-        <v>542.8424045800001</v>
+        <v>541.11311275</v>
       </c>
       <c r="Q76">
-        <v>908.9424045800001</v>
+        <v>907.2131127500001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2106420133313581</v>
+        <v>0.2165746307777309</v>
       </c>
       <c r="T76">
-        <v>1.594148254763005</v>
+        <v>1.651521199664501</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.242030201461138</v>
+        <v>5.172136465441656</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08317615769443273</v>
+        <v>0.08293999192271236</v>
       </c>
       <c r="C77">
-        <v>1468.272596041555</v>
+        <v>1428.333395091904</v>
       </c>
       <c r="D77">
-        <v>4251.947596041555</v>
+        <v>4256.681395091904</v>
       </c>
       <c r="E77">
-        <v>2670.375</v>
+        <v>2715.048</v>
       </c>
       <c r="F77">
-        <v>3350.475</v>
+        <v>3395.148</v>
       </c>
       <c r="G77">
         <v>566.8</v>
@@ -7595,28 +7595,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M77">
-        <v>185.2812675</v>
+        <v>187.7516844</v>
       </c>
       <c r="N77">
-        <v>773.0187325000001</v>
+        <v>770.5483156</v>
       </c>
       <c r="O77">
-        <v>231.90561975</v>
+        <v>231.16449468</v>
       </c>
       <c r="P77">
-        <v>541.11311275</v>
+        <v>539.3838209200001</v>
       </c>
       <c r="Q77">
-        <v>907.2131127500001</v>
+        <v>905.4838209200001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2165746307777309</v>
+        <v>0.2230016330113015</v>
       </c>
       <c r="T77">
-        <v>1.651521199664501</v>
+        <v>1.713675223307789</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.172136465441656</v>
+        <v>5.104082038264792</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08293999192271236</v>
+        <v>0.08270382615099196</v>
       </c>
       <c r="C78">
-        <v>1428.333395091904</v>
+        <v>1388.404746402875</v>
       </c>
       <c r="D78">
-        <v>4256.681395091904</v>
+        <v>4261.425746402875</v>
       </c>
       <c r="E78">
-        <v>2715.048</v>
+        <v>2759.721</v>
       </c>
       <c r="F78">
-        <v>3395.148</v>
+        <v>3439.821</v>
       </c>
       <c r="G78">
         <v>566.8</v>
@@ -7677,28 +7677,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M78">
-        <v>187.7516844</v>
+        <v>190.2221013</v>
       </c>
       <c r="N78">
-        <v>770.5483156</v>
+        <v>768.0778987000001</v>
       </c>
       <c r="O78">
-        <v>231.16449468</v>
+        <v>230.42336961</v>
       </c>
       <c r="P78">
-        <v>539.3838209200001</v>
+        <v>537.6545290900001</v>
       </c>
       <c r="Q78">
-        <v>905.4838209200001</v>
+        <v>903.7545290900001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2230016330113015</v>
+        <v>0.2299875050043129</v>
       </c>
       <c r="T78">
-        <v>1.713675223307789</v>
+        <v>1.781233944659188</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.104082038264792</v>
+        <v>5.037795258547068</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08270382615099196</v>
+        <v>0.08246766037927157</v>
       </c>
       <c r="C79">
-        <v>1388.404746402875</v>
+        <v>1348.486685297401</v>
       </c>
       <c r="D79">
-        <v>4261.425746402875</v>
+        <v>4266.180685297401</v>
       </c>
       <c r="E79">
-        <v>2759.721</v>
+        <v>2804.394</v>
       </c>
       <c r="F79">
-        <v>3439.821</v>
+        <v>3484.494</v>
       </c>
       <c r="G79">
         <v>566.8</v>
@@ -7759,28 +7759,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M79">
-        <v>190.2221013</v>
+        <v>192.6925182</v>
       </c>
       <c r="N79">
-        <v>768.0778987000001</v>
+        <v>765.6074818000001</v>
       </c>
       <c r="O79">
-        <v>230.42336961</v>
+        <v>229.68224454</v>
       </c>
       <c r="P79">
-        <v>537.6545290900001</v>
+        <v>535.92523726</v>
       </c>
       <c r="Q79">
-        <v>903.7545290900001</v>
+        <v>902.02523726</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2299875050043129</v>
+        <v>0.2376084562694163</v>
       </c>
       <c r="T79">
-        <v>1.781233944659188</v>
+        <v>1.854934367951625</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.037795258547068</v>
+        <v>4.973208139847746</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08246766037927157</v>
+        <v>0.08223149460755119</v>
       </c>
       <c r="C80">
-        <v>1348.486685297401</v>
+        <v>1308.579247256248</v>
       </c>
       <c r="D80">
-        <v>4266.180685297401</v>
+        <v>4270.946247256248</v>
       </c>
       <c r="E80">
-        <v>2804.394</v>
+        <v>2849.067</v>
       </c>
       <c r="F80">
-        <v>3484.494</v>
+        <v>3529.167</v>
       </c>
       <c r="G80">
         <v>566.8</v>
@@ -7841,28 +7841,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M80">
-        <v>192.6925182</v>
+        <v>195.1629351</v>
       </c>
       <c r="N80">
-        <v>765.6074818000001</v>
+        <v>763.1370649</v>
       </c>
       <c r="O80">
-        <v>229.68224454</v>
+        <v>228.94111947</v>
       </c>
       <c r="P80">
-        <v>535.92523726</v>
+        <v>534.1959454300001</v>
       </c>
       <c r="Q80">
-        <v>902.02523726</v>
+        <v>900.2959454300001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2376084562694163</v>
+        <v>0.2459552124169105</v>
       </c>
       <c r="T80">
-        <v>1.854934367951625</v>
+        <v>1.935653879176674</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.973208139847746</v>
+        <v>4.910256138077521</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08223149460755119</v>
+        <v>0.0819953288358308</v>
       </c>
       <c r="C81">
-        <v>1308.579247256248</v>
+        <v>1268.682467918895</v>
       </c>
       <c r="D81">
-        <v>4270.946247256248</v>
+        <v>4275.722467918895</v>
       </c>
       <c r="E81">
-        <v>2849.067</v>
+        <v>2893.74</v>
       </c>
       <c r="F81">
-        <v>3529.167</v>
+        <v>3573.84</v>
       </c>
       <c r="G81">
         <v>566.8</v>
@@ -7923,28 +7923,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M81">
-        <v>195.1629351</v>
+        <v>197.633352</v>
       </c>
       <c r="N81">
-        <v>763.1370649</v>
+        <v>760.6666480000001</v>
       </c>
       <c r="O81">
-        <v>228.94111947</v>
+        <v>228.1999944</v>
       </c>
       <c r="P81">
-        <v>534.1959454300001</v>
+        <v>532.4666536000001</v>
       </c>
       <c r="Q81">
-        <v>900.2959454300001</v>
+        <v>898.5666536000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2459552124169105</v>
+        <v>0.255136644179154</v>
       </c>
       <c r="T81">
-        <v>1.935653879176674</v>
+        <v>2.024445341524227</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.910256138077521</v>
+        <v>4.848877936351553</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.0819953288358308</v>
+        <v>0.08175916306411041</v>
       </c>
       <c r="C82">
-        <v>1268.682467918895</v>
+        <v>1228.796383084421</v>
       </c>
       <c r="D82">
-        <v>4275.722467918895</v>
+        <v>4280.509383084422</v>
       </c>
       <c r="E82">
-        <v>2893.74</v>
+        <v>2938.413</v>
       </c>
       <c r="F82">
-        <v>3573.84</v>
+        <v>3618.513</v>
       </c>
       <c r="G82">
         <v>566.8</v>
@@ -8005,28 +8005,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M82">
-        <v>197.633352</v>
+        <v>200.1037689</v>
       </c>
       <c r="N82">
-        <v>760.6666480000001</v>
+        <v>758.1962311</v>
       </c>
       <c r="O82">
-        <v>228.1999944</v>
+        <v>227.45886933</v>
       </c>
       <c r="P82">
-        <v>532.4666536000001</v>
+        <v>530.73736177</v>
       </c>
       <c r="Q82">
-        <v>898.5666536000001</v>
+        <v>896.83736177</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.255136644179154</v>
+        <v>0.2652845424426865</v>
       </c>
       <c r="T82">
-        <v>2.024445341524227</v>
+        <v>2.122583273592577</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.848877936351553</v>
+        <v>4.789015245779311</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08175916306411041</v>
+        <v>0.08152299729239004</v>
       </c>
       <c r="C83">
-        <v>1228.796383084421</v>
+        <v>1188.921028712404</v>
       </c>
       <c r="D83">
-        <v>4280.509383084422</v>
+        <v>4285.307028712405</v>
       </c>
       <c r="E83">
-        <v>2938.413</v>
+        <v>2983.086000000001</v>
       </c>
       <c r="F83">
-        <v>3618.513</v>
+        <v>3663.186000000001</v>
       </c>
       <c r="G83">
         <v>566.8</v>
@@ -8087,28 +8087,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M83">
-        <v>200.1037689</v>
+        <v>202.5741858</v>
       </c>
       <c r="N83">
-        <v>758.1962311</v>
+        <v>755.7258142000001</v>
       </c>
       <c r="O83">
-        <v>227.45886933</v>
+        <v>226.71774426</v>
       </c>
       <c r="P83">
-        <v>530.73736177</v>
+        <v>529.00806994</v>
       </c>
       <c r="Q83">
-        <v>896.83736177</v>
+        <v>895.1080699400001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2652845424426865</v>
+        <v>0.2765599849577225</v>
       </c>
       <c r="T83">
-        <v>2.122583273592577</v>
+        <v>2.231625420335187</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.789015245779311</v>
+        <v>4.730612620830783</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08152299729239004</v>
+        <v>0.08128683152066965</v>
       </c>
       <c r="C84">
-        <v>1188.921028712404</v>
+        <v>1149.056440923819</v>
       </c>
       <c r="D84">
-        <v>4285.307028712405</v>
+        <v>4290.115440923819</v>
       </c>
       <c r="E84">
-        <v>2983.086000000001</v>
+        <v>3027.759</v>
       </c>
       <c r="F84">
-        <v>3663.186000000001</v>
+        <v>3707.859</v>
       </c>
       <c r="G84">
         <v>566.8</v>
@@ -8169,28 +8169,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M84">
-        <v>202.5741858</v>
+        <v>205.0446027</v>
       </c>
       <c r="N84">
-        <v>755.7258142000001</v>
+        <v>753.2553973</v>
       </c>
       <c r="O84">
-        <v>226.71774426</v>
+        <v>225.97661919</v>
       </c>
       <c r="P84">
-        <v>529.00806994</v>
+        <v>527.2787781100001</v>
       </c>
       <c r="Q84">
-        <v>895.1080699400001</v>
+        <v>893.3787781100001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2765599849577225</v>
+        <v>0.2891619501215862</v>
       </c>
       <c r="T84">
-        <v>2.231625420335187</v>
+        <v>2.353496054929868</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.730612620830783</v>
+        <v>4.673617288049689</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08128683152066965</v>
+        <v>0.08105066574894926</v>
       </c>
       <c r="C85">
-        <v>1149.056440923819</v>
+        <v>1109.202656001937</v>
       </c>
       <c r="D85">
-        <v>4290.115440923819</v>
+        <v>4294.934656001938</v>
       </c>
       <c r="E85">
-        <v>3027.759</v>
+        <v>3072.432000000001</v>
       </c>
       <c r="F85">
-        <v>3707.859</v>
+        <v>3752.532000000001</v>
       </c>
       <c r="G85">
         <v>566.8</v>
@@ -8251,28 +8251,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M85">
-        <v>205.0446027</v>
+        <v>207.5150196</v>
       </c>
       <c r="N85">
-        <v>753.2553973</v>
+        <v>750.7849804</v>
       </c>
       <c r="O85">
-        <v>225.97661919</v>
+        <v>225.23549412</v>
       </c>
       <c r="P85">
-        <v>527.2787781100001</v>
+        <v>525.54948628</v>
       </c>
       <c r="Q85">
-        <v>893.3787781100001</v>
+        <v>891.64948628</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2891619501215862</v>
+        <v>0.303339160930933</v>
       </c>
       <c r="T85">
-        <v>2.353496054929868</v>
+        <v>2.490600518848886</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.673617288049689</v>
+        <v>4.617978987001478</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08105066574894927</v>
+        <v>0.08081449997722889</v>
       </c>
       <c r="C86">
-        <v>1109.202656001938</v>
+        <v>1069.359710393255</v>
       </c>
       <c r="D86">
-        <v>4294.934656001938</v>
+        <v>4299.764710393255</v>
       </c>
       <c r="E86">
-        <v>3072.432</v>
+        <v>3117.105</v>
       </c>
       <c r="F86">
-        <v>3752.532</v>
+        <v>3797.205</v>
       </c>
       <c r="G86">
         <v>566.8</v>
@@ -8333,28 +8333,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M86">
-        <v>207.5150196</v>
+        <v>209.9854365</v>
       </c>
       <c r="N86">
-        <v>750.7849804</v>
+        <v>748.3145635000001</v>
       </c>
       <c r="O86">
-        <v>225.23549412</v>
+        <v>224.49436905</v>
       </c>
       <c r="P86">
-        <v>525.54948628</v>
+        <v>523.82019445</v>
       </c>
       <c r="Q86">
-        <v>891.64948628</v>
+        <v>889.9201944500001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3033391609309329</v>
+        <v>0.3194066665148592</v>
       </c>
       <c r="T86">
-        <v>2.490600518848884</v>
+        <v>2.645985577957104</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.617978987001479</v>
+        <v>4.563649822448521</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08081449997722889</v>
+        <v>0.0805783342055085</v>
       </c>
       <c r="C87">
-        <v>1069.359710393255</v>
+        <v>1029.527640708397</v>
       </c>
       <c r="D87">
-        <v>4299.764710393255</v>
+        <v>4304.605640708397</v>
       </c>
       <c r="E87">
-        <v>3117.105</v>
+        <v>3161.778</v>
       </c>
       <c r="F87">
-        <v>3797.205</v>
+        <v>3841.878</v>
       </c>
       <c r="G87">
         <v>566.8</v>
@@ -8415,28 +8415,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M87">
-        <v>209.9854365</v>
+        <v>212.4558534</v>
       </c>
       <c r="N87">
-        <v>748.3145635000001</v>
+        <v>745.8441466</v>
       </c>
       <c r="O87">
-        <v>224.49436905</v>
+        <v>223.75324398</v>
       </c>
       <c r="P87">
-        <v>523.82019445</v>
+        <v>522.0909026200001</v>
       </c>
       <c r="Q87">
-        <v>889.9201944500001</v>
+        <v>888.1909026200001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3194066665148592</v>
+        <v>0.3377695300393463</v>
       </c>
       <c r="T87">
-        <v>2.645985577957104</v>
+        <v>2.823568502652211</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.563649822448521</v>
+        <v>4.510584126838653</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.0805783342055085</v>
+        <v>0.08186466843378812</v>
       </c>
       <c r="C88">
-        <v>1029.527640708397</v>
+        <v>958.6185390223332</v>
       </c>
       <c r="D88">
-        <v>4304.605640708397</v>
+        <v>4278.369539022333</v>
       </c>
       <c r="E88">
-        <v>3161.778</v>
+        <v>3206.451</v>
       </c>
       <c r="F88">
-        <v>3841.878</v>
+        <v>3886.551</v>
       </c>
       <c r="G88">
         <v>566.8</v>
@@ -8497,45 +8497,45 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M88">
-        <v>212.4558534</v>
+        <v>224.6426478</v>
       </c>
       <c r="N88">
-        <v>745.8441466</v>
+        <v>733.6573522000001</v>
       </c>
       <c r="O88">
-        <v>223.75324398</v>
+        <v>220.09720566</v>
       </c>
       <c r="P88">
-        <v>522.0909026200001</v>
+        <v>513.5601465400001</v>
       </c>
       <c r="Q88">
-        <v>888.1909026200001</v>
+        <v>879.6601465400001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3377695300393463</v>
+        <v>0.3589574494906778</v>
       </c>
       <c r="T88">
-        <v>2.823568502652211</v>
+        <v>3.028471877300412</v>
       </c>
       <c r="U88">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V88">
         <v>0.3</v>
       </c>
       <c r="W88">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y88">
-        <v>4.510584126838653</v>
+        <v>4.265886328286058</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08186466843378812</v>
+        <v>0.08164600266206773</v>
       </c>
       <c r="C89">
-        <v>958.6185390223332</v>
+        <v>918.3828657370123</v>
       </c>
       <c r="D89">
-        <v>4278.369539022333</v>
+        <v>4282.806865737012</v>
       </c>
       <c r="E89">
-        <v>3206.451</v>
+        <v>3251.124</v>
       </c>
       <c r="F89">
-        <v>3886.551</v>
+        <v>3931.224</v>
       </c>
       <c r="G89">
         <v>566.8</v>
@@ -8579,28 +8579,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M89">
-        <v>224.6426478</v>
+        <v>227.2247472</v>
       </c>
       <c r="N89">
-        <v>733.6573522000001</v>
+        <v>731.0752528</v>
       </c>
       <c r="O89">
-        <v>220.09720566</v>
+        <v>219.32257584</v>
       </c>
       <c r="P89">
-        <v>513.5601465400001</v>
+        <v>511.75267696</v>
       </c>
       <c r="Q89">
-        <v>879.6601465400001</v>
+        <v>877.8526769600001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3589574494906778</v>
+        <v>0.3836766888505644</v>
       </c>
       <c r="T89">
-        <v>3.028471877300412</v>
+        <v>3.267525814389981</v>
       </c>
       <c r="U89">
         <v>0.0578</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.265886328286058</v>
+        <v>4.217410347282806</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08164600266206773</v>
+        <v>0.08142733689034734</v>
       </c>
       <c r="C90">
-        <v>918.3828657370123</v>
+        <v>878.156406387428</v>
       </c>
       <c r="D90">
-        <v>4282.806865737012</v>
+        <v>4287.253406387428</v>
       </c>
       <c r="E90">
-        <v>3251.124</v>
+        <v>3295.797</v>
       </c>
       <c r="F90">
-        <v>3931.224</v>
+        <v>3975.897</v>
       </c>
       <c r="G90">
         <v>566.8</v>
@@ -8661,28 +8661,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M90">
-        <v>227.2247472</v>
+        <v>229.8068466</v>
       </c>
       <c r="N90">
-        <v>731.0752528</v>
+        <v>728.4931534</v>
       </c>
       <c r="O90">
-        <v>219.32257584</v>
+        <v>218.54794602</v>
       </c>
       <c r="P90">
-        <v>511.75267696</v>
+        <v>509.94520738</v>
       </c>
       <c r="Q90">
-        <v>877.8526769600001</v>
+        <v>876.04520738</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3836766888505644</v>
+        <v>0.412890335366794</v>
       </c>
       <c r="T90">
-        <v>3.267525814389981</v>
+        <v>3.550044103677652</v>
       </c>
       <c r="U90">
         <v>0.0578</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.217410347282806</v>
+        <v>4.17002371416727</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08142733689034734</v>
+        <v>0.08120867111862695</v>
       </c>
       <c r="C91">
-        <v>878.156406387428</v>
+        <v>837.9391897019736</v>
       </c>
       <c r="D91">
-        <v>4287.253406387428</v>
+        <v>4291.709189701974</v>
       </c>
       <c r="E91">
-        <v>3295.797</v>
+        <v>3340.47</v>
       </c>
       <c r="F91">
-        <v>3975.897</v>
+        <v>4020.57</v>
       </c>
       <c r="G91">
         <v>566.8</v>
@@ -8743,28 +8743,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M91">
-        <v>229.8068466</v>
+        <v>232.388946</v>
       </c>
       <c r="N91">
-        <v>728.4931534</v>
+        <v>725.911054</v>
       </c>
       <c r="O91">
-        <v>218.54794602</v>
+        <v>217.7733162</v>
       </c>
       <c r="P91">
-        <v>509.94520738</v>
+        <v>508.1377378</v>
       </c>
       <c r="Q91">
-        <v>876.04520738</v>
+        <v>874.2377378000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.412890335366794</v>
+        <v>0.4479467111862696</v>
       </c>
       <c r="T91">
-        <v>3.550044103677652</v>
+        <v>3.889066050822858</v>
       </c>
       <c r="U91">
         <v>0.0578</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.17002371416727</v>
+        <v>4.123690117343189</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08120867111862695</v>
+        <v>0.08099000534690656</v>
       </c>
       <c r="C92">
-        <v>837.9391897019736</v>
+        <v>797.7312445285979</v>
       </c>
       <c r="D92">
-        <v>4291.709189701974</v>
+        <v>4296.174244528598</v>
       </c>
       <c r="E92">
-        <v>3340.47</v>
+        <v>3385.143</v>
       </c>
       <c r="F92">
-        <v>4020.57</v>
+        <v>4065.243</v>
       </c>
       <c r="G92">
         <v>566.8</v>
@@ -8825,28 +8825,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M92">
-        <v>232.388946</v>
+        <v>234.9710454</v>
       </c>
       <c r="N92">
-        <v>725.911054</v>
+        <v>723.3289546000001</v>
       </c>
       <c r="O92">
-        <v>217.7733162</v>
+        <v>216.99868638</v>
       </c>
       <c r="P92">
-        <v>508.1377378</v>
+        <v>506.3302682200001</v>
       </c>
       <c r="Q92">
-        <v>874.2377378000001</v>
+        <v>872.4302682200001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4479467111862696</v>
+        <v>0.4907933927434064</v>
       </c>
       <c r="T92">
-        <v>3.889066050822858</v>
+        <v>4.303426208444776</v>
       </c>
       <c r="U92">
         <v>0.0578</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.123690117343189</v>
+        <v>4.078374841328428</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08099000534690656</v>
+        <v>0.08077133957518617</v>
       </c>
       <c r="C93">
-        <v>797.7312445285979</v>
+        <v>757.5325998354274</v>
       </c>
       <c r="D93">
-        <v>4296.174244528598</v>
+        <v>4300.648599835427</v>
       </c>
       <c r="E93">
-        <v>3385.143</v>
+        <v>3429.816</v>
       </c>
       <c r="F93">
-        <v>4065.243</v>
+        <v>4109.916</v>
       </c>
       <c r="G93">
         <v>566.8</v>
@@ -8907,28 +8907,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M93">
-        <v>234.9710454</v>
+        <v>237.5531448</v>
       </c>
       <c r="N93">
-        <v>723.3289546000001</v>
+        <v>720.7468552</v>
       </c>
       <c r="O93">
-        <v>216.99868638</v>
+        <v>216.22405656</v>
       </c>
       <c r="P93">
-        <v>506.3302682200001</v>
+        <v>504.52279864</v>
       </c>
       <c r="Q93">
-        <v>872.4302682200001</v>
+        <v>870.62279864</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4907933927434064</v>
+        <v>0.5443517446898275</v>
       </c>
       <c r="T93">
-        <v>4.303426208444776</v>
+        <v>4.821376405472175</v>
       </c>
       <c r="U93">
         <v>0.0578</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.078374841328428</v>
+        <v>4.034044680009641</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08077133957518617</v>
+        <v>0.08283117380346579</v>
       </c>
       <c r="C94">
-        <v>757.5325998354274</v>
+        <v>671.0771371334331</v>
       </c>
       <c r="D94">
-        <v>4300.648599835427</v>
+        <v>4258.866137133433</v>
       </c>
       <c r="E94">
-        <v>3429.816</v>
+        <v>3474.489</v>
       </c>
       <c r="F94">
-        <v>4109.916</v>
+        <v>4154.589</v>
       </c>
       <c r="G94">
         <v>566.8</v>
@@ -8989,45 +8989,45 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M94">
-        <v>237.5531448</v>
+        <v>254.6763057</v>
       </c>
       <c r="N94">
-        <v>720.7468552</v>
+        <v>703.6236943000001</v>
       </c>
       <c r="O94">
-        <v>216.22405656</v>
+        <v>211.08710829</v>
       </c>
       <c r="P94">
-        <v>504.52279864</v>
+        <v>492.5365860100001</v>
       </c>
       <c r="Q94">
-        <v>870.62279864</v>
+        <v>858.6365860100001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5443517446898275</v>
+        <v>0.6132124829066545</v>
       </c>
       <c r="T94">
-        <v>4.821376405472175</v>
+        <v>5.487312373078829</v>
       </c>
       <c r="U94">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V94">
         <v>0.3</v>
       </c>
       <c r="W94">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y94">
-        <v>4.034044680009641</v>
+        <v>3.762815694086771</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08283117380346579</v>
+        <v>0.08263700803174541</v>
       </c>
       <c r="C95">
-        <v>671.0771371334331</v>
+        <v>630.3079804368299</v>
       </c>
       <c r="D95">
-        <v>4258.866137133433</v>
+        <v>4262.76998043683</v>
       </c>
       <c r="E95">
-        <v>3474.489</v>
+        <v>3519.162000000001</v>
       </c>
       <c r="F95">
-        <v>4154.589</v>
+        <v>4199.262000000001</v>
       </c>
       <c r="G95">
         <v>566.8</v>
@@ -9071,28 +9071,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M95">
-        <v>254.6763057</v>
+        <v>257.4147606</v>
       </c>
       <c r="N95">
-        <v>703.6236943000001</v>
+        <v>700.8852394</v>
       </c>
       <c r="O95">
-        <v>211.08710829</v>
+        <v>210.26557182</v>
       </c>
       <c r="P95">
-        <v>492.5365860100001</v>
+        <v>490.6196675800001</v>
       </c>
       <c r="Q95">
-        <v>858.6365860100001</v>
+        <v>856.7196675800001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6132124829066545</v>
+        <v>0.7050268005290908</v>
       </c>
       <c r="T95">
-        <v>5.487312373078829</v>
+        <v>6.37522699655437</v>
       </c>
       <c r="U95">
         <v>0.0613</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.762815694086771</v>
+        <v>3.722785739894358</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08263700803174541</v>
+        <v>0.08244284226002502</v>
       </c>
       <c r="C96">
-        <v>630.3079804368299</v>
+        <v>589.5459871374505</v>
       </c>
       <c r="D96">
-        <v>4262.76998043683</v>
+        <v>4266.680987137451</v>
       </c>
       <c r="E96">
-        <v>3519.162000000001</v>
+        <v>3563.835</v>
       </c>
       <c r="F96">
-        <v>4199.262000000001</v>
+        <v>4243.935</v>
       </c>
       <c r="G96">
         <v>566.8</v>
@@ -9153,28 +9153,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M96">
-        <v>257.4147606</v>
+        <v>260.1532155</v>
       </c>
       <c r="N96">
-        <v>700.8852394</v>
+        <v>698.1467845</v>
       </c>
       <c r="O96">
-        <v>210.26557182</v>
+        <v>209.44403535</v>
       </c>
       <c r="P96">
-        <v>490.6196675800001</v>
+        <v>488.70274915</v>
       </c>
       <c r="Q96">
-        <v>856.7196675800001</v>
+        <v>854.80274915</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7050268005290908</v>
+        <v>0.8335668452005016</v>
       </c>
       <c r="T96">
-        <v>6.37522699655437</v>
+        <v>7.618307469420128</v>
       </c>
       <c r="U96">
         <v>0.0613</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.722785739894358</v>
+        <v>3.68359852157968</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08244284226002502</v>
+        <v>0.08224867648830464</v>
       </c>
       <c r="C97">
-        <v>589.5459871374505</v>
+        <v>548.7911769702223</v>
       </c>
       <c r="D97">
-        <v>4266.680987137451</v>
+        <v>4270.599176970222</v>
       </c>
       <c r="E97">
-        <v>3563.835</v>
+        <v>3608.508</v>
       </c>
       <c r="F97">
-        <v>4243.935</v>
+        <v>4288.608</v>
       </c>
       <c r="G97">
         <v>566.8</v>
@@ -9235,28 +9235,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M97">
-        <v>260.1532155</v>
+        <v>262.8916704</v>
       </c>
       <c r="N97">
-        <v>698.1467845</v>
+        <v>695.4083296000001</v>
       </c>
       <c r="O97">
-        <v>209.44403535</v>
+        <v>208.62249888</v>
       </c>
       <c r="P97">
-        <v>488.70274915</v>
+        <v>486.7858307200001</v>
       </c>
       <c r="Q97">
-        <v>854.80274915</v>
+        <v>852.8858307200001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8335668452005016</v>
+        <v>1.026376912207618</v>
       </c>
       <c r="T97">
-        <v>7.618307469420128</v>
+        <v>9.482928178718765</v>
       </c>
       <c r="U97">
         <v>0.0613</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.68359852157968</v>
+        <v>3.645227703646559</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08224867648830464</v>
+        <v>0.08205451071658426</v>
       </c>
       <c r="C98">
-        <v>548.7911769702223</v>
+        <v>508.0435697426356</v>
       </c>
       <c r="D98">
-        <v>4270.599176970222</v>
+        <v>4274.524569742635</v>
       </c>
       <c r="E98">
-        <v>3608.508</v>
+        <v>3653.181</v>
       </c>
       <c r="F98">
-        <v>4288.608</v>
+        <v>4333.281</v>
       </c>
       <c r="G98">
         <v>566.8</v>
@@ -9317,28 +9317,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M98">
-        <v>262.8916704</v>
+        <v>265.6301253</v>
       </c>
       <c r="N98">
-        <v>695.4083296000001</v>
+        <v>692.6698747</v>
       </c>
       <c r="O98">
-        <v>208.62249888</v>
+        <v>207.80096241</v>
       </c>
       <c r="P98">
-        <v>486.7858307200001</v>
+        <v>484.86891229</v>
       </c>
       <c r="Q98">
-        <v>852.8858307200001</v>
+        <v>850.96891229</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.026376912207615</v>
+        <v>1.347727023886141</v>
       </c>
       <c r="T98">
-        <v>9.482928178718739</v>
+        <v>12.59062936088312</v>
       </c>
       <c r="U98">
         <v>0.0613</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.645227703646559</v>
+        <v>3.607648036598656</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08205451071658426</v>
+        <v>0.08186034494486388</v>
       </c>
       <c r="C99">
-        <v>508.0435697426356</v>
+        <v>467.3031853350694</v>
       </c>
       <c r="D99">
-        <v>4274.524569742635</v>
+        <v>4278.457185335069</v>
       </c>
       <c r="E99">
-        <v>3653.181</v>
+        <v>3697.854</v>
       </c>
       <c r="F99">
-        <v>4333.281</v>
+        <v>4377.954</v>
       </c>
       <c r="G99">
         <v>566.8</v>
@@ -9399,28 +9399,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M99">
-        <v>265.6301253</v>
+        <v>268.3685802</v>
       </c>
       <c r="N99">
-        <v>692.6698747</v>
+        <v>689.9314198000001</v>
       </c>
       <c r="O99">
-        <v>207.80096241</v>
+        <v>206.97942594</v>
       </c>
       <c r="P99">
-        <v>484.86891229</v>
+        <v>482.95199386</v>
       </c>
       <c r="Q99">
-        <v>850.96891229</v>
+        <v>849.05199386</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.347727023886141</v>
+        <v>1.990427247243192</v>
       </c>
       <c r="T99">
-        <v>12.59062936088312</v>
+        <v>18.80603172521188</v>
       </c>
       <c r="U99">
         <v>0.0613</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.607648036598656</v>
+        <v>3.570835301531323</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08186034494486388</v>
+        <v>0.08166617917314348</v>
       </c>
       <c r="C100">
-        <v>467.3031853350694</v>
+        <v>426.5700437011346</v>
       </c>
       <c r="D100">
-        <v>4278.457185335069</v>
+        <v>4282.397043701135</v>
       </c>
       <c r="E100">
-        <v>3697.854</v>
+        <v>3742.527</v>
       </c>
       <c r="F100">
-        <v>4377.954</v>
+        <v>4422.627</v>
       </c>
       <c r="G100">
         <v>566.8</v>
@@ -9481,28 +9481,28 @@
         <v>958.3000000000001</v>
       </c>
       <c r="M100">
-        <v>268.3685802</v>
+        <v>271.1070351</v>
       </c>
       <c r="N100">
-        <v>689.9314198000001</v>
+        <v>687.1929649000001</v>
       </c>
       <c r="O100">
-        <v>206.97942594</v>
+        <v>206.15788947</v>
       </c>
       <c r="P100">
-        <v>482.95199386</v>
+        <v>481.0350754300001</v>
       </c>
       <c r="Q100">
-        <v>849.05199386</v>
+        <v>847.1350754300001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.990427247243192</v>
+        <v>3.918527917314345</v>
       </c>
       <c r="T100">
-        <v>18.80603172521188</v>
+        <v>37.45223881819817</v>
       </c>
       <c r="U100">
         <v>0.0613</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.570835301531323</v>
+        <v>3.534766258081512</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08166617917314348</v>
-      </c>
-      <c r="C101">
-        <v>426.5700437011346</v>
-      </c>
-      <c r="D101">
-        <v>4282.397043701135</v>
-      </c>
-      <c r="E101">
-        <v>3742.527</v>
-      </c>
-      <c r="F101">
-        <v>4422.627</v>
-      </c>
-      <c r="G101">
-        <v>566.8</v>
-      </c>
-      <c r="H101">
-        <v>3787.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1324.4</v>
-      </c>
-      <c r="K101">
-        <v>366.1</v>
-      </c>
-      <c r="L101">
-        <v>958.3000000000001</v>
-      </c>
-      <c r="M101">
-        <v>271.1070351</v>
-      </c>
-      <c r="N101">
-        <v>687.1929649000001</v>
-      </c>
-      <c r="O101">
-        <v>206.15788947</v>
-      </c>
-      <c r="P101">
-        <v>481.0350754300001</v>
-      </c>
-      <c r="Q101">
-        <v>847.1350754300001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.918527917314345</v>
-      </c>
-      <c r="T101">
-        <v>37.45223881819817</v>
-      </c>
-      <c r="U101">
-        <v>0.0613</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.04291</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba1/BB+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.534766258081512</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
